--- a/docs/oc-regiones/insumos-y-dispositivos-medicos/aysen.xlsx
+++ b/docs/oc-regiones/insumos-y-dispositivos-medicos/aysen.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2143</v>
+        <v>2124.85</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3902.87</v>
+        <v>3869.82</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>801.22</v>
+        <v>793.22</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2953.83</v>
+        <v>2924.35</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1648.94</v>
+        <v>1631.67</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1983.97</v>
+        <v>1973.11</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>15259.62</v>
+        <v>15314.08</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2432.91</v>
+        <v>2441.6</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1006.74</v>
+        <v>1010.33</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1945.01</v>
+        <v>1951.4</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2880.58</v>
+        <v>2875.47</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1312.48</v>
+        <v>1310.15</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>815.53</v>
+        <v>814.08</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2521.68</v>
+        <v>2517.21</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1523.59</v>
+        <v>1521.23</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>8386.110000000001</v>
+        <v>8429.42</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3944.01</v>
+        <v>3964.38</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3373.42</v>
+        <v>3390.85</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>826.25</v>
+        <v>830.51</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1854.34</v>
+        <v>1867.43</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>772.84</v>
+        <v>763.03</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1340.46</v>
+        <v>1337.56</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1656.01</v>
+        <v>1641.99</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1039.12</v>
+        <v>1040.45</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>976</v>
+        <v>951.08</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>4410.4</v>
+        <v>4324.38</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>848.11</v>
+        <v>831.5700000000001</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>4597.16</v>
+        <v>4531.27</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>849.1900000000001</v>
+        <v>836.95</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1524.61</v>
+        <v>1502.64</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>8877.690000000001</v>
+        <v>8871.629999999999</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1747.38</v>
+        <v>1741.38</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2665.49</v>
+        <v>2656.34</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>805.62</v>
+        <v>825.21</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1931.4</v>
+        <v>1978.37</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2527.27</v>
+        <v>2591.16</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>3715.53</v>
+        <v>3828.2</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>927.6799999999999</v>
+        <v>923.77</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>8019.97</v>
+        <v>8092.92</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1932.95</v>
+        <v>1950.53</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2171.7</v>
+        <v>2169.46</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1794.62</v>
+        <v>1784.05</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>4272.73</v>
+        <v>4256.24</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>993.96</v>
+        <v>1022.83</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1896.38</v>
+        <v>1927.63</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>8260.35</v>
+        <v>8396.5</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>770.34</v>
+        <v>784.3</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>3128.69</v>
+        <v>3131.38</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>3989.81</v>
+        <v>4006.29</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>9802.299999999999</v>
+        <v>9689.139999999999</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1765.59</v>
+        <v>1755.45</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>3148.3</v>
+        <v>3128.13</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>3661.97</v>
+        <v>3646.19</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2596.34</v>
+        <v>2535.92</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>4258.3</v>
+        <v>4122.52</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>4453.13</v>
+        <v>4311.13</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3502.26</v>
+        <v>3390.59</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3977.12</v>
+        <v>3850.3</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>811.11</v>
+        <v>785.24</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>934.36</v>
+        <v>904.5700000000001</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1463.17</v>
+        <v>1416.51</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>15699.39</v>
+        <v>15389.78</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>970.34</v>
+        <v>974.37</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1783.5</v>
+        <v>1780.52</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>14565.43</v>
+        <v>14744.69</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>9910.43</v>
+        <v>10042.36</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3041.8</v>
+        <v>3081.49</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1988</v>
+        <v>2025.6</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>915.13</v>
+        <v>932.4400000000001</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>837.85</v>
+        <v>853.6900000000001</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2910.77</v>
+        <v>2943.87</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1919.66</v>
+        <v>1936.96</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>4082.76</v>
+        <v>4119.54</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1348.06</v>
+        <v>1356.69</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>828</v>
+        <v>833.3</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>29820.04</v>
+        <v>29913.86</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1458.3</v>
+        <v>1462.89</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>8258.629999999999</v>
+        <v>8284.610000000001</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>1821.5</v>
+        <v>1827.23</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1177.43</v>
+        <v>1181.13</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>9140.17</v>
+        <v>9159.110000000001</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>4823.48</v>
+        <v>4802.76</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>828.85</v>
+        <v>825.29</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2649.01</v>
+        <v>2637.63</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1814.82</v>
+        <v>1824.59</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>17483.35</v>
+        <v>17577.5</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>10345.11</v>
+        <v>10400.82</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>4844.11</v>
+        <v>4870.2</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>8558.73</v>
+        <v>8623.559999999999</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>2825.73</v>
+        <v>2847.14</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>10184.5</v>
+        <v>10158.79</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>880.74</v>
+        <v>878.52</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>954.95</v>
+        <v>952.54</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>5344.73</v>
+        <v>5395.51</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>3940.65</v>
+        <v>3978.09</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1705.43</v>
+        <v>1721.64</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>3316.32</v>
+        <v>3347.83</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>923.75</v>
+        <v>932.53</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1903.29</v>
+        <v>1917.47</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>8577.02</v>
+        <v>8491.49</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>4402.02</v>
+        <v>4382.72</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1755.4</v>
+        <v>1747.7</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>15653.88</v>
+        <v>15585.27</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>883.25</v>
+        <v>873.64</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>2306.07</v>
+        <v>2300.37</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2578.55</v>
+        <v>2608.8</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>1744.23</v>
+        <v>1773.73</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>4191.4</v>
+        <v>4262.29</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>1374.14</v>
+        <v>1350.92</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>2114.22</v>
+        <v>2084.21</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>4257.28</v>
+        <v>4196.86</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>3030.77</v>
+        <v>2987.76</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>3857.28</v>
+        <v>3802.54</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>936.21</v>
+        <v>923.35</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>881.66</v>
+        <v>869.55</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1618.26</v>
+        <v>1596.03</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>826.09</v>
+        <v>814.73</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>803.4</v>
+        <v>792.36</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>838.42</v>
+        <v>826.9</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1127.91</v>
+        <v>1112.41</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>1974.59</v>
+        <v>1947.45</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>2066.43</v>
+        <v>2053.61</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>1309.31</v>
+        <v>1328.8</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>15993.93</v>
+        <v>16354.64</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>876.88</v>
+        <v>896.66</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1328.57</v>
+        <v>1358.53</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>1267.3</v>
+        <v>1263.95</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>827.9299999999999</v>
+        <v>811.72</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>1157.17</v>
+        <v>1140.02</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>29783.45</v>
+        <v>29342.18</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>12764.76</v>
+        <v>12575.64</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>809.8200000000001</v>
+        <v>797.8200000000001</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>793.3099999999999</v>
+        <v>777.01</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>1630.51</v>
+        <v>1646.91</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1152.89</v>
+        <v>1147.05</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>1868.84</v>
+        <v>1859.37</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>815.67</v>
+        <v>811.54</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>833.8200000000001</v>
+        <v>835.6</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>2031.81</v>
+        <v>2036.47</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>8447.280000000001</v>
+        <v>8466.65</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>7323.77</v>
+        <v>7340.57</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>19090.52</v>
+        <v>19134.3</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>2115.69</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>799.39</v>
+        <v>796.87</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1001.82</v>
+        <v>998.65</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>1190.65</v>
+        <v>1188.06</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1068.76</v>
+        <v>1066.43</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>11714.4</v>
+        <v>11688.91</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>794.91</v>
+        <v>782.08</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>1687.27</v>
+        <v>1667.64</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1563.79</v>
+        <v>1555.13</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>1344.87</v>
+        <v>1337.42</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>1203.1</v>
+        <v>1197.19</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>3368.64</v>
+        <v>3352.08</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>6255.18</v>
+        <v>6297.05</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/insumos-y-dispositivos-medicos/aysen.xlsx
+++ b/docs/oc-regiones/insumos-y-dispositivos-medicos/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M156"/>
+  <dimension ref="A1:M160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>418-3379-CM25</t>
+          <t>3950-3427-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>Jocelyn</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.226.228-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2124.85</v>
+        <v>771.28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>418-3380-CM25</t>
+          <t>3950-3482-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3869.82</v>
+        <v>770.78</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1691-3025-CM25</t>
+          <t>886182-91-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>793.22</v>
+        <v>5626.52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1691-3029-CM25</t>
+          <t>3949-236-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>COMERCIAL EXPRESS DENT LIMITADA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>78.378.160-3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2924.35</v>
+        <v>3173.63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>418-3512-CM25</t>
+          <t>418-3379-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>EXXIMMED 2000 SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>78.060.400-k</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1631.67</v>
+        <v>2124.85</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1691-2888-CM25</t>
+          <t>418-3380-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1973.11</v>
+        <v>3869.82</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1691-3117-CM25</t>
+          <t>1691-3029-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.237.150-0</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>15314.08</v>
+        <v>2924.35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4609-534-CM25</t>
+          <t>1691-3025-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2441.6</v>
+        <v>793.22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1692-2967-CM25</t>
+          <t>418-3512-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>EXXIMMED 2000 SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>78.060.400-k</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1010.33</v>
+        <v>1631.67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1274667-656-CM25</t>
+          <t>1691-2888-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>COMERCIAL EXPRESS DENT LIMITADA</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>78.378.160-3</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1951.4</v>
+        <v>1973.11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1691-2678-CM25</t>
+          <t>1691-3117-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>77.237.150-0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2875.47</v>
+        <v>15314.08</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1691-3018-CM25</t>
+          <t>4609-534-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.240.400-9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1310.15</v>
+        <v>2441.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1691-3191-CM25</t>
+          <t>1692-2967-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>814.08</v>
+        <v>1010.33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1691-3192-CM25</t>
+          <t>1274667-656-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>COMERCIAL EXPRESS DENT LIMITADA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>78.378.160-3</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2517.21</v>
+        <v>1951.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1691-3015-CM25</t>
+          <t>1691-3192-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1521.23</v>
+        <v>2517.21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1691-3032-CM25</t>
+          <t>1691-3191-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>8429.42</v>
+        <v>814.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1691-3036-CM25</t>
+          <t>1691-2678-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3964.38</v>
+        <v>2875.47</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1691-3176-CM25</t>
+          <t>1691-3018-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMERCIAL LIMAX SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.719.400-5</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3390.85</v>
+        <v>1310.15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2151-432-CM25</t>
+          <t>1691-3015-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>830.51</v>
+        <v>1521.23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>907-210-CM25</t>
+          <t>1691-3032-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1867.43</v>
+        <v>8429.42</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1691-3195-CM25</t>
+          <t>1691-3036-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>763.03</v>
+        <v>3964.38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1691-3367-CM25</t>
+          <t>1691-3176-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>COMERCIAL LIMAX SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.719.400-5</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1337.56</v>
+        <v>3390.85</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1691-3043-CM25</t>
+          <t>2151-432-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1641.99</v>
+        <v>830.51</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1691-3551-CM25</t>
+          <t>907-210-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>EXXIMMED 2000 SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>78.060.400-k</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1040.45</v>
+        <v>1867.43</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1691-3698-CM25</t>
+          <t>1691-3195-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>951.08</v>
+        <v>763.03</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1691-3521-CM25</t>
+          <t>1691-3367-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>4324.38</v>
+        <v>1337.56</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1691-3643-CM25</t>
+          <t>1691-3043-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>831.5700000000001</v>
+        <v>1641.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1691-3041-CM25</t>
+          <t>1691-3551-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>EXXIMMED 2000 SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>78.060.400-k</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>4531.27</v>
+        <v>1040.45</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1691-21-CM26</t>
+          <t>1691-3698-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>836.95</v>
+        <v>951.08</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1691-3039-CM25</t>
+          <t>1691-3521-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1502.64</v>
+        <v>4324.38</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1691-3693-CM25</t>
+          <t>1691-3643-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>8871.629999999999</v>
+        <v>831.5700000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1691-3560-CM25</t>
+          <t>1691-3041-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1741.38</v>
+        <v>4531.27</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1691-3655-CM25</t>
+          <t>1691-3039-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2656.34</v>
+        <v>1502.64</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3950-95-CM26</t>
+          <t>1691-21-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Jocelyn</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.226.228-2</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>825.21</v>
+        <v>836.95</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3950-98-CM26</t>
+          <t>1691-3693-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1978.37</v>
+        <v>8871.629999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1691-161-CM26</t>
+          <t>1691-3560-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>MEDISAN CHILE SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.426.475-4</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2591.16</v>
+        <v>1741.38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>418-204-CM26</t>
+          <t>1691-3655-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>3828.2</v>
+        <v>2656.34</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1691-248-CM26</t>
+          <t>3950-98-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>923.77</v>
+        <v>1978.37</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>418-207-CM26</t>
+          <t>3950-95-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>Jocelyn</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>76.226.228-2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>8092.92</v>
+        <v>825.21</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>418-146-CM26</t>
+          <t>1691-161-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>MEDISAN CHILE SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>76.426.475-4</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1950.53</v>
+        <v>2591.16</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3950-281-CM26</t>
+          <t>418-204-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>ISI-MED SPA</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>77.430.568-8</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2169.46</v>
+        <v>3828.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1691-208-CM26</t>
+          <t>1691-248-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1784.05</v>
+        <v>923.77</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1691-257-CM26</t>
+          <t>418-146-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>4256.24</v>
+        <v>1950.53</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>707426-43-CM26</t>
+          <t>418-207-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1022.83</v>
+        <v>8092.92</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1691-333-CM26</t>
+          <t>3950-281-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>ISI-MED SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>77.430.568-8</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1927.63</v>
+        <v>2169.46</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1691-413-CM26</t>
+          <t>1691-208-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA HOSPITALMARKET SPA</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>77.910.467-2</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>8396.5</v>
+        <v>1784.05</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>854-27-CM26</t>
+          <t>1691-257-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>784.3</v>
+        <v>4256.24</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1691-444-CM26</t>
+          <t>707426-43-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>3131.38</v>
+        <v>1022.83</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1691-486-CM26</t>
+          <t>1691-333-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>4006.29</v>
+        <v>1927.63</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1691-528-CM26</t>
+          <t>1691-413-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>CLINICON SPA</t>
+          <t>COMERCIALIZADORA HOSPITALMARKET SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>77.070.635-1</t>
+          <t>77.910.467-2</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>9689.139999999999</v>
+        <v>8396.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1691-597-CM26</t>
+          <t>854-27-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1755.45</v>
+        <v>784.3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>418-903-CM26</t>
+          <t>1691-444-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>3128.13</v>
+        <v>3131.38</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1691-594-CM26</t>
+          <t>1691-486-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>3646.19</v>
+        <v>4006.29</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1691-627-CM26</t>
+          <t>1691-528-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>CLINICON SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>77.070.635-1</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2535.92</v>
+        <v>9689.139999999999</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1274667-135-CM26</t>
+          <t>1691-597-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>4122.52</v>
+        <v>1755.45</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1691-622-CM26</t>
+          <t>418-903-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>EXXIMMED 2000 SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>78.060.400-k</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>4311.13</v>
+        <v>3128.13</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1691-610-CM26</t>
+          <t>1691-594-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3390.59</v>
+        <v>3646.19</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1691-619-CM26</t>
+          <t>1691-627-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3850.3</v>
+        <v>2535.92</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>418-992-CM26</t>
+          <t>1274667-135-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>77.237.150-0</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>785.24</v>
+        <v>4122.52</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1691-347-CM26</t>
+          <t>1691-622-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>EXXIMMED 2000 SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>78.060.400-k</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>904.5700000000001</v>
+        <v>4311.13</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>418-1001-CM26</t>
+          <t>1691-619-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1416.51</v>
+        <v>3850.3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1691-665-CM26</t>
+          <t>418-1001-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>77.237.150-0</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>15389.78</v>
+        <v>1416.51</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2151-112-CM26</t>
+          <t>418-992-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>77.237.150-0</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>974.37</v>
+        <v>785.24</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>418-1141-CM26</t>
+          <t>1691-347-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1780.52</v>
+        <v>904.5700000000001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1691-713-CM26</t>
+          <t>1691-610-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>14744.69</v>
+        <v>3390.59</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1691-739-CM26</t>
+          <t>1691-665-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>77.237.150-0</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>10042.36</v>
+        <v>15389.78</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2151-124-CM26</t>
+          <t>2151-112-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>77.025.316-0</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3081.49</v>
+        <v>974.37</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1274667-145-CM26</t>
+          <t>418-1141-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2025.6</v>
+        <v>1780.52</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1691-695-CM26</t>
+          <t>1691-713-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>GERMÁN BERNARDO BEHNKE GUTIÉRREZ</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>5.892.120-3</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>932.4400000000001</v>
+        <v>14744.69</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1691-714-CM26</t>
+          <t>1691-739-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>853.6900000000001</v>
+        <v>10042.36</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3950-555-CM26</t>
+          <t>2151-124-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>77.025.316-0</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2943.87</v>
+        <v>3081.49</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>418-1268-CM26</t>
+          <t>1274667-145-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1936.96</v>
+        <v>2025.6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>886182-129-CM26</t>
+          <t>1691-695-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>GERMÁN BERNARDO BEHNKE GUTIÉRREZ</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>5.892.120-3</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>4119.54</v>
+        <v>932.4400000000001</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1274667-144-CM26</t>
+          <t>1691-714-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>77.025.316-0</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1356.69</v>
+        <v>853.6900000000001</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>886182-131-CM26</t>
+          <t>3950-555-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>833.3</v>
+        <v>2943.87</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1691-808-CM26</t>
+          <t>418-1268-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>29913.86</v>
+        <v>1936.96</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2151-132-CM26</t>
+          <t>886182-129-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>Universidad de Aysen</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>77.025.316-0</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1462.89</v>
+        <v>4119.54</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>734-240-CM26</t>
+          <t>1274667-144-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>77.025.316-0</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>8284.610000000001</v>
+        <v>1356.69</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1691-795-CM26</t>
+          <t>886182-131-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>Universidad de Aysen</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>1827.23</v>
+        <v>833.3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>418-1223-CM26</t>
+          <t>1691-808-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1181.13</v>
+        <v>29913.86</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1691-796-CM26</t>
+          <t>2151-132-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5419,12 +5419,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>77.025.316-0</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>9159.110000000001</v>
+        <v>1462.89</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1691-824-CM26</t>
+          <t>418-1223-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>4802.76</v>
+        <v>1181.13</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1691-856-CM26</t>
+          <t>1691-795-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>825.29</v>
+        <v>1827.23</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1691-857-CM26</t>
+          <t>734-240-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2637.63</v>
+        <v>8284.610000000001</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1691-938-CM26</t>
+          <t>1691-796-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>CONVATEC CHILE S.A.</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.020.266-5</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1824.59</v>
+        <v>9159.110000000001</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1691-837-CM26</t>
+          <t>1691-824-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>17577.5</v>
+        <v>4802.76</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1691-797-CM26</t>
+          <t>1691-856-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>10400.82</v>
+        <v>825.29</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1691-799-CM26</t>
+          <t>1691-857-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>HEMISFERIO SUR S.A.</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>96.533.330-4</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>4870.2</v>
+        <v>2637.63</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1691-865-CM26</t>
+          <t>1691-797-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>8623.559999999999</v>
+        <v>10400.82</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1691-866-CM26</t>
+          <t>1691-799-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>2847.14</v>
+        <v>4870.2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1691-941-CM26</t>
+          <t>1691-837-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>CLINICON SPA</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>77.070.635-1</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>10158.79</v>
+        <v>17577.5</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>418-1502-CM26</t>
+          <t>1691-938-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>CONVATEC CHILE S.A.</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.020.266-5</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>878.52</v>
+        <v>1824.59</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1691-977-CM26</t>
+          <t>1691-865-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>952.54</v>
+        <v>8623.559999999999</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1691-992-CM26</t>
+          <t>1691-866-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>HEMISFERIO SUR S.A.</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.533.330-4</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>5395.51</v>
+        <v>2847.14</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1691-982-CM26</t>
+          <t>1691-941-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>CLINICON SPA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>77.070.635-1</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>3978.09</v>
+        <v>10158.79</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1691-994-CM26</t>
+          <t>418-1502-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1721.64</v>
+        <v>878.52</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1691-923-CM26</t>
+          <t>1691-977-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>3347.83</v>
+        <v>952.54</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>3765-399-CM26</t>
+          <t>1691-992-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>932.53</v>
+        <v>5395.51</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1274667-181-CM26</t>
+          <t>1691-982-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>COMERCIAL EXPRESS DENT LIMITADA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>78.378.160-3</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1917.47</v>
+        <v>3978.09</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1691-960-CM26</t>
+          <t>1691-994-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>8491.49</v>
+        <v>1721.64</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1691-704-CM26</t>
+          <t>1691-923-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>4382.72</v>
+        <v>3347.83</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1691-1074-CM26</t>
+          <t>3765-399-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1747.7</v>
+        <v>932.53</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1691-1082-CM26</t>
+          <t>1274667-181-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>COMERCIAL EXPRESS DENT LIMITADA</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>78.378.160-3</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>15585.27</v>
+        <v>1917.47</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>418-1541-CM26</t>
+          <t>1691-960-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6812,7 +6812,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6822,12 +6822,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>873.64</v>
+        <v>8491.49</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>3950-722-CM26</t>
+          <t>1691-704-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>2300.37</v>
+        <v>4382.72</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1691-1147-CM26</t>
+          <t>1691-1074-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2608.8</v>
+        <v>1747.7</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1691-1038-CM26</t>
+          <t>1691-1082-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6990,12 +6990,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>1773.73</v>
+        <v>15585.27</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1691-743-CM26</t>
+          <t>418-1541-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>4262.29</v>
+        <v>873.64</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2151-211-CM26</t>
+          <t>3950-722-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7112,12 +7112,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>COMERCIAL LIMAX SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>76.719.400-5</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>1350.92</v>
+        <v>2300.37</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1691-1101-CM26</t>
+          <t>1691-1147-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7203,12 +7203,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>2084.21</v>
+        <v>2608.8</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1691-1103-CM26</t>
+          <t>1691-1038-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>PTM EMERGENCIA</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>76.612.187-K</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>4196.86</v>
+        <v>1773.73</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1691-1200-CM26</t>
+          <t>1691-743-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2987.76</v>
+        <v>4262.29</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1691-1201-CM26</t>
+          <t>2151-211-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>MEDISAN CHILE SPA</t>
+          <t>COMERCIAL LIMAX SPA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>76.426.475-4</t>
+          <t>76.719.400-5</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>3802.54</v>
+        <v>1350.92</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>418-1886-CM26</t>
+          <t>1691-1101-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>923.35</v>
+        <v>2084.21</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>418-1885-CM26</t>
+          <t>1691-1103-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>MEDISAN CHILE SPA</t>
+          <t>PTM EMERGENCIA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>76.426.475-4</t>
+          <t>76.612.187-K</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>869.55</v>
+        <v>4196.86</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>418-1884-CM26</t>
+          <t>1691-1200-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7554,12 +7554,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1596.03</v>
+        <v>2987.76</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>418-1882-CM26</t>
+          <t>1691-1201-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>MEDISAN CHILE SPA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>76.426.475-4</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7645,13 +7645,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>814.73</v>
+        <v>3802.54</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>418-1844-CM26</t>
+          <t>418-1886-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>792.36</v>
+        <v>923.35</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>418-1831-CM26</t>
+          <t>418-1885-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>MEDISAN CHILE SPA</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.426.475-4</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7767,13 +7767,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>826.9</v>
+        <v>869.55</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>418-1826-CM26</t>
+          <t>418-1884-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7813,12 +7813,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1112.41</v>
+        <v>1596.03</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>418-1825-CM26</t>
+          <t>418-1882-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7874,12 +7874,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>1947.45</v>
+        <v>814.73</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1691-1221-CM26</t>
+          <t>418-1844-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7950,13 +7950,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>2053.61</v>
+        <v>792.36</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1274667-199-CM26</t>
+          <t>418-1826-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>DIFEM LABORATORIOS S A</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>79.581.120-6</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>1328.8</v>
+        <v>1112.41</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1691-1280-CM26</t>
+          <t>418-1825-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>77.237.150-0</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>16354.64</v>
+        <v>1947.45</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2151-222-CM26</t>
+          <t>418-1831-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>DELTAMED LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>76.512.686-k</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>896.66</v>
+        <v>826.9</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2151-223-CM26</t>
+          <t>1691-1221-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>MEDIPLEX S A</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>86.383.300-0</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8194,13 +8194,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1358.53</v>
+        <v>2053.61</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1691-1169-CM26</t>
+          <t>1274667-199-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8240,12 +8240,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>DIFEM LABORATORIOS S A</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>79.581.120-6</t>
         </is>
       </c>
       <c r="K128" t="inlineStr"/>
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>1263.95</v>
+        <v>1328.8</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1274667-224-CM26</t>
+          <t>1691-1280-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>DELTAMED LIMITADA</t>
+          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>76.512.686-k</t>
+          <t>77.237.150-0</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -8316,13 +8316,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>811.72</v>
+        <v>16354.64</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1691-1222-CM26</t>
+          <t>2151-222-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8347,12 +8347,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8362,12 +8362,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>DELTAMED LIMITADA</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>76.512.686-k</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>1140.02</v>
+        <v>896.66</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1691-1272-CM26</t>
+          <t>2151-223-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>MEDIPLEX S A</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>86.383.300-0</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>29342.18</v>
+        <v>1358.53</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1691-1275-CM26</t>
+          <t>1691-1169-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8459,7 +8459,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>CONVATEC CHILE S.A.</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>76.020.266-5</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>12575.64</v>
+        <v>1263.95</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1692-423-CM26</t>
+          <t>1274667-224-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>DELTAMED LIMITADA</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>76.512.686-k</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8560,13 +8560,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>797.8200000000001</v>
+        <v>811.72</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>3765-561-CM26</t>
+          <t>1691-1222-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>MADEGOM S.A.</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>84.609.600-0</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8621,13 +8621,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>777.01</v>
+        <v>1140.02</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1691-1285-CM26</t>
+          <t>1691-1272-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8637,12 +8637,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8682,13 +8682,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>1646.91</v>
+        <v>29342.18</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1692-451-CM26</t>
+          <t>1691-1275-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8698,12 +8698,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>CONVATEC CHILE S.A.</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.020.266-5</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1147.05</v>
+        <v>12575.64</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>707426-105-CM26</t>
+          <t>1692-423-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>1859.37</v>
+        <v>797.8200000000001</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>707426-103-CM26</t>
+          <t>3765-561-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8850,12 +8850,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>DIFEM LABORATORIOS S A</t>
+          <t>MADEGOM S.A.</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>79.581.120-6</t>
+          <t>84.609.600-0</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -8865,13 +8865,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>811.54</v>
+        <v>777.01</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1691-1391-CM26</t>
+          <t>1691-1285-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -8926,13 +8926,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>835.6</v>
+        <v>1646.91</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1691-1271-CM26</t>
+          <t>1692-451-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -8987,13 +8987,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>2036.47</v>
+        <v>1147.05</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1691-1286-CM26</t>
+          <t>707426-105-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9033,12 +9033,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
@@ -9048,13 +9048,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>8466.65</v>
+        <v>1859.37</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1691-1295-CM26</t>
+          <t>707426-103-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>DIFEM LABORATORIOS S A</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>79.581.120-6</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -9109,13 +9109,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>7340.57</v>
+        <v>811.54</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1691-1414-CM26</t>
+          <t>1691-1391-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -9170,13 +9170,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>19134.3</v>
+        <v>835.6</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>418-2221-CM26</t>
+          <t>1691-1271-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>2109</v>
+        <v>2036.47</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1691-1479-CM26</t>
+          <t>1691-1286-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -9292,13 +9292,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>796.87</v>
+        <v>8466.65</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1691-1486-CM26</t>
+          <t>1691-1295-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9353,13 +9353,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>998.65</v>
+        <v>7340.57</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>418-2228-CM26</t>
+          <t>1691-1414-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9384,12 +9384,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9399,12 +9399,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -9414,13 +9414,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>1188.06</v>
+        <v>19134.3</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>418-2237-CM26</t>
+          <t>418-2221-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9475,13 +9475,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1066.43</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>3950-1038-CM26</t>
+          <t>1691-1479-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9496,22 +9496,22 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>11688.91</v>
+        <v>796.87</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1274667-282-CM26</t>
+          <t>1691-1486-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9567,12 +9567,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9582,12 +9582,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9597,13 +9597,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>782.08</v>
+        <v>998.65</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1691-1531-CM26</t>
+          <t>418-2228-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9658,13 +9658,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>1667.64</v>
+        <v>1188.06</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>418-2297-CM26</t>
+          <t>418-2237-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>Comercial LBF Limitada</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9719,13 +9719,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1555.13</v>
+        <v>1066.43</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>418-2305-CM26</t>
+          <t>3950-1038-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9750,12 +9750,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>IMPORTADORA MEGA MARKET LIMITADA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>76.012.551-2</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9780,13 +9780,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>1337.42</v>
+        <v>11688.91</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1691-1587-CM26</t>
+          <t>1274667-282-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9826,12 +9826,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Medisan Limitada</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>77.693.540-9</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -9841,13 +9841,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>1197.19</v>
+        <v>782.08</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1691-1527-CM26</t>
+          <t>1691-1531-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9862,12 +9862,12 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -9887,12 +9887,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -9902,13 +9902,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>3352.08</v>
+        <v>1667.64</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1691-1570-CM26</t>
+          <t>418-2297-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9923,22 +9923,22 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9963,6 +9963,250 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
+        <v>1555.13</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>418-2305-CM26</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>61.602.279-2</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>IMPORTADORA MEGA MARKET LIMITADA</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>76.012.551-2</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="n">
+        <v>1337.42</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>1691-1587-CM26</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Medisan Limitada</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>77.693.540-9</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="n">
+        <v>1197.19</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>1691-1527-CM26</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>78.566.250-4</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="n">
+        <v>3352.08</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>1691-1570-CM26</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="n">
         <v>6297.05</v>
       </c>
     </row>

--- a/docs/oc-regiones/insumos-y-dispositivos-medicos/aysen.xlsx
+++ b/docs/oc-regiones/insumos-y-dispositivos-medicos/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M318"/>
+  <dimension ref="A1:M335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1002,7 +1002,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1274667-22-CM25</t>
+          <t>1691-214-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>JFV SPA</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.561.431-5</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>5913.67</v>
+        <v>2446.71</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1691-214-CM25</t>
+          <t>1274667-22-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>JFV SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>77.561.431-5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2446.71</v>
+        <v>5913.67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3950-912-CM25</t>
+          <t>418-489-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1144,17 +1144,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>984.64</v>
+        <v>5579.34</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3950-911-CM25</t>
+          <t>3950-907-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>ISI-MED SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>77.430.568-8</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2314.83</v>
+        <v>728.26</v>
       </c>
     </row>
     <row r="14">
@@ -1307,7 +1307,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3950-907-CM25</t>
+          <t>3950-911-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>ISI-MED SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.430.568-8</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>728.26</v>
+        <v>2314.83</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>418-489-CM25</t>
+          <t>3950-912-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1388,17 +1388,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>5579.34</v>
+        <v>984.64</v>
       </c>
     </row>
     <row r="17">
@@ -1734,7 +1734,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>907-31-CM25</t>
+          <t>1691-557-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2777.58</v>
+        <v>2024.36</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1691-557-CM25</t>
+          <t>907-31-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2024.36</v>
+        <v>2777.58</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1691-263-CM25</t>
+          <t>707426-15-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1891.62</v>
+        <v>2234.84</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1691-318-CM25</t>
+          <t>1691-263-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1978,7 +1978,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1691-338-CM25</t>
+          <t>1691-318-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1588.64</v>
+        <v>1891.62</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>707426-15-CM25</t>
+          <t>1691-338-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2234.84</v>
+        <v>1588.64</v>
       </c>
     </row>
     <row r="28">
@@ -2222,7 +2222,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1691-631-CM25</t>
+          <t>418-609-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>3378.79</v>
+        <v>727.5599999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1691-687-CM25</t>
+          <t>1691-631-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1922.68</v>
+        <v>3378.79</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>418-609-CM25</t>
+          <t>1691-687-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>727.5599999999999</v>
+        <v>1922.68</v>
       </c>
     </row>
     <row r="33">
@@ -2954,7 +2954,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1691-852-CM25</t>
+          <t>1691-853-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>8470.950000000001</v>
+        <v>1435.81</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1691-853-CM25</t>
+          <t>1691-852-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1435.81</v>
+        <v>8470.950000000001</v>
       </c>
     </row>
     <row r="44">
@@ -3991,7 +3991,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1691-1311-CM25</t>
+          <t>1691-1308-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3448.11</v>
+        <v>8346.129999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1691-1308-CM25</t>
+          <t>1691-1311-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>8346.129999999999</v>
+        <v>3448.11</v>
       </c>
     </row>
     <row r="61">
@@ -4723,7 +4723,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2151-189-CM25</t>
+          <t>2151-194-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>774.78</v>
+        <v>745.6799999999999</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2151-194-CM25</t>
+          <t>2151-189-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>745.6799999999999</v>
+        <v>774.78</v>
       </c>
     </row>
     <row r="73">
@@ -5028,7 +5028,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>418-1882-CM25</t>
+          <t>418-1907-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>MEDISAN CHILE SPA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>76.426.475-4</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2581.3</v>
+        <v>1025.64</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>418-1907-CM25</t>
+          <t>418-1882-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>MEDISAN CHILE SPA</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.426.475-4</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1025.64</v>
+        <v>2581.3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1691-1759-CM25</t>
+          <t>3950-3759-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5170,17 +5170,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>8367.26</v>
+        <v>13455.19</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3950-3759-CM25</t>
+          <t>1691-1759-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5231,17 +5231,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>13455.19</v>
+        <v>8367.26</v>
       </c>
     </row>
     <row r="80">
@@ -5516,7 +5516,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>418-2049-CM25</t>
+          <t>1691-1545-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1175.31</v>
+        <v>1433.21</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1691-1827-CM25</t>
+          <t>1691-1628-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>5253.66</v>
+        <v>1674.97</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1691-1628-CM25</t>
+          <t>1691-1827-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1674.97</v>
+        <v>5253.66</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1691-1545-CM25</t>
+          <t>418-2049-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1433.21</v>
+        <v>1175.31</v>
       </c>
     </row>
     <row r="88">
@@ -5882,7 +5882,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1691-1859-CM25</t>
+          <t>418-1490-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1404.5</v>
+        <v>738.17</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>418-1490-CM25</t>
+          <t>1691-1859-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>738.17</v>
+        <v>1404.5</v>
       </c>
     </row>
     <row r="92">
@@ -6126,7 +6126,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1691-1961-CM25</t>
+          <t>418-2319-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2602.15</v>
+        <v>2739.35</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>418-2319-CM25</t>
+          <t>1691-1961-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>2739.35</v>
+        <v>2602.15</v>
       </c>
     </row>
     <row r="96">
@@ -6309,7 +6309,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1691-2066-CM25</t>
+          <t>1691-2035-CM25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1138.44</v>
+        <v>3388.75</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1691-2035-CM25</t>
+          <t>1691-2066-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>3388.75</v>
+        <v>1138.44</v>
       </c>
     </row>
     <row r="99">
@@ -6919,7 +6919,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1691-2324-CM25</t>
+          <t>1691-2384-CM25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>HEMISFERIO SUR S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>96.533.330-4</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>3649.62</v>
+        <v>1391.35</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1691-2385-CM25</t>
+          <t>1691-2324-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>HEMISFERIO SUR S.A.</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>96.533.330-4</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2432.51</v>
+        <v>3649.62</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1691-2384-CM25</t>
+          <t>1691-2385-CM25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1391.35</v>
+        <v>2432.51</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>418-2688-CM25</t>
+          <t>418-2690-CM25</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>1322.29</v>
+        <v>2191.18</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>418-2690-CM25</t>
+          <t>418-2688-CM25</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7203,12 +7203,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>2191.18</v>
+        <v>1322.29</v>
       </c>
     </row>
     <row r="112">
@@ -7895,7 +7895,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>418-3137-CM25</t>
+          <t>418-2980-CM25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>4189.13</v>
+        <v>3670.08</v>
       </c>
     </row>
     <row r="124">
@@ -8017,7 +8017,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>418-2980-CM25</t>
+          <t>418-3137-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>3670.08</v>
+        <v>4189.13</v>
       </c>
     </row>
     <row r="126">
@@ -8566,7 +8566,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1691-2832-CM25</t>
+          <t>1691-2926-CM25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8621,13 +8621,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>861.02</v>
+        <v>5420.72</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1691-2926-CM25</t>
+          <t>1691-2832-CM25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>5420.72</v>
+        <v>861.02</v>
       </c>
     </row>
     <row r="136">
@@ -8749,7 +8749,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1691-2651-CM25</t>
+          <t>418-3376-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>1104.9</v>
+        <v>1885.98</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>418-3376-CM25</t>
+          <t>418-3377-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8865,13 +8865,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1885.98</v>
+        <v>750.97</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>418-3377-CM25</t>
+          <t>1691-2651-CM25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8926,13 +8926,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>750.97</v>
+        <v>1104.9</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1691-3004-CM25</t>
+          <t>854-343-CM25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8987,13 +8987,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1424.41</v>
+        <v>740.0700000000001</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>854-343-CM25</t>
+          <t>1691-3004-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9048,13 +9048,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>740.0700000000001</v>
+        <v>1424.41</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>418-3380-CM25</t>
+          <t>418-3379-CM25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -9109,13 +9109,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>3869.82</v>
+        <v>2124.85</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>418-3379-CM25</t>
+          <t>418-3380-CM25</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -9170,13 +9170,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>2124.85</v>
+        <v>3869.82</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1691-3025-CM25</t>
+          <t>1691-3029-CM25</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>793.22</v>
+        <v>2924.35</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1691-3029-CM25</t>
+          <t>1691-3025-CM25</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2924.35</v>
+        <v>793.22</v>
       </c>
     </row>
     <row r="146">
@@ -9420,7 +9420,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>4609-534-CM25</t>
+          <t>1691-3117-CM25</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>77.237.150-0</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -9475,13 +9475,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>2441.6</v>
+        <v>15314.08</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1692-2967-CM25</t>
+          <t>4609-534-CM25</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>69.240.400-9</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1010.33</v>
+        <v>2441.6</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1691-3117-CM25</t>
+          <t>1692-2967-CM25</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9567,12 +9567,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9582,12 +9582,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>77.237.150-0</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>15314.08</v>
+        <v>1010.33</v>
       </c>
     </row>
     <row r="151">
@@ -9969,7 +9969,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1691-3036-CM25</t>
+          <t>1691-3032-CM25</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10009,12 +10009,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -10024,13 +10024,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>3964.38</v>
+        <v>8429.42</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1691-3176-CM25</t>
+          <t>1691-3036-CM25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>COMERCIAL LIMAX SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>76.719.400-5</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10085,13 +10085,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>3390.85</v>
+        <v>3964.38</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2151-432-CM25</t>
+          <t>1691-3176-CM25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10116,12 +10116,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10131,12 +10131,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>COMERCIAL LIMAX SPA</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>76.719.400-5</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>830.51</v>
+        <v>3390.85</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1691-3032-CM25</t>
+          <t>2151-432-CM25</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>8429.42</v>
+        <v>830.51</v>
       </c>
     </row>
     <row r="161">
@@ -10579,7 +10579,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1691-3521-CM25</t>
+          <t>1691-3643-CM25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -10634,13 +10634,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>4324.38</v>
+        <v>831.5700000000001</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1691-3643-CM25</t>
+          <t>1691-3521-CM25</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>831.5700000000001</v>
+        <v>4324.38</v>
       </c>
     </row>
     <row r="169">
@@ -10762,7 +10762,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1691-21-CM26</t>
+          <t>1691-3039-CM25</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10802,12 +10802,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -10817,13 +10817,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>836.95</v>
+        <v>1502.64</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1691-3039-CM25</t>
+          <t>1691-21-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>1502.64</v>
+        <v>836.95</v>
       </c>
     </row>
     <row r="172">
@@ -10924,7 +10924,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -11412,7 +11412,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -11656,7 +11656,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -11900,7 +11900,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -12348,7 +12348,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1691-347-CM26</t>
+          <t>1274667-135-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K196" t="inlineStr"/>
@@ -12403,13 +12403,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>904.5700000000001</v>
+        <v>4122.52</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>418-992-CM26</t>
+          <t>1691-622-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12434,12 +12434,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
+          <t>EXXIMMED 2000 SPA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>77.237.150-0</t>
+          <t>78.060.400-k</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
@@ -12464,13 +12464,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>785.24</v>
+        <v>4311.13</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>418-1001-CM26</t>
+          <t>1691-619-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12495,12 +12495,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>1416.51</v>
+        <v>3850.3</v>
       </c>
     </row>
     <row r="199">
@@ -12592,7 +12592,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1691-619-CM26</t>
+          <t>418-1001-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K200" t="inlineStr"/>
@@ -12647,13 +12647,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>3850.3</v>
+        <v>1416.51</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1691-622-CM26</t>
+          <t>418-992-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12678,12 +12678,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>EXXIMMED 2000 SPA</t>
+          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>78.060.400-k</t>
+          <t>77.237.150-0</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
@@ -12708,13 +12708,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>4311.13</v>
+        <v>785.24</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1274667-135-CM26</t>
+          <t>1691-347-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12739,12 +12739,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12754,12 +12754,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>4122.52</v>
+        <v>904.5700000000001</v>
       </c>
     </row>
     <row r="203">
@@ -12937,7 +12937,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -12998,7 +12998,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -13059,7 +13059,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -13141,7 +13141,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1691-695-CM26</t>
+          <t>1274667-145-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13166,12 +13166,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13181,12 +13181,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>GERMÁN BERNARDO BEHNKE GUTIÉRREZ</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>5.892.120-3</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>932.4400000000001</v>
+        <v>2025.6</v>
       </c>
     </row>
     <row r="210">
@@ -13263,7 +13263,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1274667-145-CM26</t>
+          <t>1691-695-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13288,12 +13288,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13303,12 +13303,12 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>GERMÁN BERNARDO BEHNKE GUTIÉRREZ</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>5.892.120-3</t>
         </is>
       </c>
       <c r="K211" t="inlineStr"/>
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>2025.6</v>
+        <v>932.4400000000001</v>
       </c>
     </row>
     <row r="212">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13598,7 +13598,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13974,7 +13974,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -14096,7 +14096,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -14340,7 +14340,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -15154,7 +15154,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1691-1074-CM26</t>
+          <t>1691-704-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
@@ -15209,13 +15209,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>1747.7</v>
+        <v>4382.72</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1691-1082-CM26</t>
+          <t>1691-1074-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15255,12 +15255,12 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K243" t="inlineStr"/>
@@ -15270,13 +15270,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>15585.27</v>
+        <v>1747.7</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1691-704-CM26</t>
+          <t>1691-1082-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15316,12 +15316,12 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K244" t="inlineStr"/>
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>4382.72</v>
+        <v>15585.27</v>
       </c>
     </row>
     <row r="245">
@@ -15560,7 +15560,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -15621,7 +15621,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -15764,7 +15764,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1691-1101-CM26</t>
+          <t>1691-1200-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -15804,12 +15804,12 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K252" t="inlineStr"/>
@@ -15819,13 +15819,13 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>2084.21</v>
+        <v>2987.76</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1691-1103-CM26</t>
+          <t>1691-1101-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>PTM EMERGENCIA</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>76.612.187-K</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K253" t="inlineStr"/>
@@ -15880,13 +15880,13 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>4196.86</v>
+        <v>2084.21</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1691-1200-CM26</t>
+          <t>1691-1103-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -15926,12 +15926,12 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>PTM Emergencia</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>76.612.187-K</t>
         </is>
       </c>
       <c r="K254" t="inlineStr"/>
@@ -15941,13 +15941,13 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>2987.76</v>
+        <v>4196.86</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>418-1886-CM26</t>
+          <t>418-1885-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -15987,12 +15987,12 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>MEDISAN CHILE SPA</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>76.426.475-4</t>
         </is>
       </c>
       <c r="K255" t="inlineStr"/>
@@ -16002,13 +16002,13 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>923.35</v>
+        <v>869.55</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>418-1885-CM26</t>
+          <t>418-1884-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>MEDISAN CHILE SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>76.426.475-4</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K256" t="inlineStr"/>
@@ -16063,13 +16063,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>869.55</v>
+        <v>1596.03</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>418-1884-CM26</t>
+          <t>418-1882-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16109,12 +16109,12 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K257" t="inlineStr"/>
@@ -16124,13 +16124,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>1596.03</v>
+        <v>814.73</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>418-1882-CM26</t>
+          <t>418-1886-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16170,12 +16170,12 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K258" t="inlineStr"/>
@@ -16185,13 +16185,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>814.73</v>
+        <v>923.35</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>418-1826-CM26</t>
+          <t>418-1831-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K259" t="inlineStr"/>
@@ -16246,13 +16246,13 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>1112.41</v>
+        <v>826.9</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>418-1831-CM26</t>
+          <t>418-1826-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16292,12 +16292,12 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K260" t="inlineStr"/>
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>826.9</v>
+        <v>1112.41</v>
       </c>
     </row>
     <row r="261">
@@ -16557,7 +16557,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2151-222-CM26</t>
+          <t>1691-1280-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -16582,12 +16582,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16597,12 +16597,12 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>DELTAMED LIMITADA</t>
+          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>76.512.686-k</t>
+          <t>77.237.150-0</t>
         </is>
       </c>
       <c r="K265" t="inlineStr"/>
@@ -16612,13 +16612,13 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>896.66</v>
+        <v>16354.64</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2151-223-CM26</t>
+          <t>2151-222-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -16658,12 +16658,12 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>MEDIPLEX S A</t>
+          <t>DELTAMED LIMITADA</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>86.383.300-0</t>
+          <t>76.512.686-k</t>
         </is>
       </c>
       <c r="K266" t="inlineStr"/>
@@ -16673,13 +16673,13 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>1358.53</v>
+        <v>896.66</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1691-1280-CM26</t>
+          <t>2151-223-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -16704,12 +16704,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -16719,12 +16719,12 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
+          <t>MEDIPLEX S A</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>77.237.150-0</t>
+          <t>86.383.300-0</t>
         </is>
       </c>
       <c r="K267" t="inlineStr"/>
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>16354.64</v>
+        <v>1358.53</v>
       </c>
     </row>
     <row r="268">
@@ -16780,7 +16780,7 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
@@ -16862,7 +16862,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1691-1222-CM26</t>
+          <t>1691-1275-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -16902,12 +16902,12 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>CONVATEC CHILE S.A.</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>76.020.266-5</t>
         </is>
       </c>
       <c r="K270" t="inlineStr"/>
@@ -16917,13 +16917,13 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>1140.02</v>
+        <v>12575.64</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1691-1272-CM26</t>
+          <t>1692-423-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -16948,12 +16948,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -16963,12 +16963,12 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K271" t="inlineStr"/>
@@ -16978,13 +16978,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>29342.18</v>
+        <v>797.8200000000001</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1691-1275-CM26</t>
+          <t>1691-1222-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17024,12 +17024,12 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>CONVATEC CHILE S.A.</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>76.020.266-5</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K272" t="inlineStr"/>
@@ -17039,13 +17039,13 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>12575.64</v>
+        <v>1140.02</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>1692-423-CM26</t>
+          <t>1691-1272-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17070,12 +17070,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -17085,12 +17085,12 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K273" t="inlineStr"/>
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>797.8200000000001</v>
+        <v>29342.18</v>
       </c>
     </row>
     <row r="274">
@@ -17512,7 +17512,7 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
@@ -17756,7 +17756,7 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
@@ -17817,7 +17817,7 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
@@ -18000,7 +18000,7 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>Comercial LBF Limitada</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
@@ -18224,7 +18224,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -18326,7 +18326,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1691-1587-CM26</t>
+          <t>1691-1527-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -18346,7 +18346,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -18366,12 +18366,12 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>Medisan Limitada</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>77.693.540-9</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K294" t="inlineStr"/>
@@ -18381,13 +18381,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>1197.19</v>
+        <v>3352.08</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>1691-1527-CM26</t>
+          <t>1691-1587-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -18407,7 +18407,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -18427,12 +18427,12 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>Medisan Limitada</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>77.693.540-9</t>
         </is>
       </c>
       <c r="K295" t="inlineStr"/>
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>3352.08</v>
+        <v>1197.19</v>
       </c>
     </row>
     <row r="296">
@@ -18468,7 +18468,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -18997,7 +18997,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2151-324-CM26</t>
+          <t>2151-318-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -19037,12 +19037,12 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K305" t="inlineStr"/>
@@ -19052,13 +19052,13 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>861.02</v>
+        <v>1295.9</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2151-320-CM26</t>
+          <t>2151-319-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -19098,12 +19098,12 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>DELTAMED LIMITADA</t>
+          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>76.512.686-k</t>
+          <t>77.025.316-0</t>
         </is>
       </c>
       <c r="K306" t="inlineStr"/>
@@ -19113,13 +19113,13 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>1843.42</v>
+        <v>1194.84</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2151-318-CM26</t>
+          <t>2151-320-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -19159,12 +19159,12 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>DELTAMED LIMITADA</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>76.512.686-k</t>
         </is>
       </c>
       <c r="K307" t="inlineStr"/>
@@ -19174,13 +19174,13 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>1295.9</v>
+        <v>1843.42</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2151-319-CM26</t>
+          <t>2151-324-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -19200,7 +19200,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -19220,12 +19220,12 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>77.025.316-0</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K308" t="inlineStr"/>
@@ -19235,7 +19235,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>1194.84</v>
+        <v>861.02</v>
       </c>
     </row>
     <row r="309">
@@ -19444,7 +19444,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -19668,7 +19668,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>1691-1738-CM26</t>
+          <t>1691-1736-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -19708,12 +19708,12 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>CONVATEC CHILE S.A.</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.020.266-5</t>
         </is>
       </c>
       <c r="K316" t="inlineStr"/>
@@ -19723,13 +19723,13 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>2366.71</v>
+        <v>1299.9</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>1691-1736-CM26</t>
+          <t>1691-1738-CM26</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -19769,12 +19769,12 @@
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>CONVATEC CHILE S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>76.020.266-5</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K317" t="inlineStr"/>
@@ -19784,7 +19784,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>1299.9</v>
+        <v>2366.71</v>
       </c>
     </row>
     <row r="318">
@@ -19846,6 +19846,1043 @@
       </c>
       <c r="M318" s="2" t="n">
         <v>3824.47</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>1691-1829-CM26</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>Pulsar Medical</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>76.923.737-2</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr"/>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M319" s="2" t="n">
+        <v>1693.6</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>1691-1756-CM26</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr"/>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M320" s="2" t="n">
+        <v>1412.46</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>854-198-CM26</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>NEMO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>76.215.260-6</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr"/>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M321" s="2" t="n">
+        <v>991.64</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>1691-1854-CM26</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>77.237.150-0</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr"/>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M322" s="2" t="n">
+        <v>15587.49</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>1691-1743-CM26</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>B BRAUN MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>96.756.540-7</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr"/>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M323" s="2" t="n">
+        <v>24596.91</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>1691-1877-CM26</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>B BRAUN MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>96.756.540-7</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr"/>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M324" s="2" t="n">
+        <v>3383.96</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>1692-643-CM26</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>61.602.292-k</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr"/>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M325" s="2" t="n">
+        <v>1040.73</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>1692-644-CM26</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>61.602.292-k</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>77.190.880-2</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr"/>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M326" s="2" t="n">
+        <v>766.34</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2151-363-CM26</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>61.602.293-8</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>NEMO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>76.215.260-6</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr"/>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M327" s="2" t="n">
+        <v>907.33</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>1691-1923-CM26</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>CLINICON SPA</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>77.070.635-1</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr"/>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M328" s="2" t="n">
+        <v>5355</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>1274667-356-CM26</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>62.000.940-7</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>REUTTER S A</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr"/>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M329" s="2" t="n">
+        <v>2797.5</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>1691-1920-CM26</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr"/>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M330" s="2" t="n">
+        <v>818.91</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>418-3059-CM26</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>61.602.279-2</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>MEDISAN CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>76.426.475-4</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr"/>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M331" s="2" t="n">
+        <v>830.2</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>1691-1774-CM26</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr"/>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M332" s="2" t="n">
+        <v>1395.42</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>418-3097-CM26</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>61.602.279-2</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>MEDIPLEX S A</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>86.383.300-0</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr"/>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M333" s="2" t="n">
+        <v>940.38</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>1691-2057-CM26</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr"/>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M334" s="2" t="n">
+        <v>15236.34</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>418-3235-CM26</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>61.602.279-2</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>TECNIKA S A</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr"/>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M335" s="2" t="n">
+        <v>1556.5</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/insumos-y-dispositivos-medicos/aysen.xlsx
+++ b/docs/oc-regiones/insumos-y-dispositivos-medicos/aysen.xlsx
@@ -684,7 +684,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1062,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1127,11 @@
           <t>77.561.431-5</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1253,11 @@
           <t>77.430.568-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1501,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1566,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1875,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1940,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2249,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2314,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2501,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2688,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2753,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2879,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3127,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3192,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3318,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +3993,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4119,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4306,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4493,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4802,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4867,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +4993,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5119,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5245,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5371,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5802,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6538,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +6847,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +6973,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7587,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7652,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7717,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +7782,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8030,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8400,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8465,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8530,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8656,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8721,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +8786,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +8912,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9160,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9225,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9412,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9477,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9603,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +9729,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10038,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10225,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10473,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10538,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +10847,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11156,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11526,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11652,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +11717,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +11782,11 @@
           <t>77.430.568-8</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +11847,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +11912,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +11977,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12103,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12168,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12416,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +12664,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +12912,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13221,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13286,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13351,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13477,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +13664,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +13790,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +13916,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +13981,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14290,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14416,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +14481,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +14668,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +14855,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15164,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +15595,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +15721,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +15786,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +15912,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +15977,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16164,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16229,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +16416,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +16481,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +16668,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +16794,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17164,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +17473,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +17782,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +17908,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18156,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18221,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +18408,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +18473,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19148,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +19335,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +19461,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +19648,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +19896,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +19961,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +20026,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +20396,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20143,7 +20583,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +20648,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +20957,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20570,7 +21022,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +21148,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +21274,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/insumos-y-dispositivos-medicos/aysen.xlsx
+++ b/docs/oc-regiones/insumos-y-dispositivos-medicos/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M335"/>
+  <dimension ref="A1:M349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1892,7 +1892,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>707426-15-CM25</t>
+          <t>1691-318-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1932,32 +1932,28 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2234.84</v>
+        <v>1891.62</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1691-263-CM25</t>
+          <t>707426-15-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1982,12 +1978,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1997,28 +1993,32 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1891.62</v>
+        <v>2234.84</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1691-318-CM25</t>
+          <t>1691-338-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2058,12 +2058,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2073,13 +2073,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1891.62</v>
+        <v>1588.64</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1691-338-CM25</t>
+          <t>1691-263-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1588.64</v>
+        <v>1891.62</v>
       </c>
     </row>
     <row r="28">
@@ -2188,7 +2188,11 @@
           <t>84.609.600-0</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2266,7 +2270,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>418-609-CM25</t>
+          <t>1691-687-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2291,12 +2295,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2306,32 +2310,28 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>727.5599999999999</v>
+        <v>1922.68</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1691-631-CM25</t>
+          <t>418-609-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2371,28 +2371,32 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3378.79</v>
+        <v>727.5599999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1691-687-CM25</t>
+          <t>1691-631-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2432,12 +2436,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2447,7 +2451,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1922.68</v>
+        <v>3378.79</v>
       </c>
     </row>
     <row r="33">
@@ -3018,7 +3022,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1691-853-CM25</t>
+          <t>1691-852-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3058,28 +3062,32 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1435.81</v>
+        <v>8470.950000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1691-852-CM25</t>
+          <t>1691-853-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3119,26 +3127,22 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>8470.950000000001</v>
+        <v>1435.81</v>
       </c>
     </row>
     <row r="44">
@@ -3518,7 +3522,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1691-1043-CM25</t>
+          <t>1691-1142-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3558,12 +3562,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>HEMISFERIO SUR S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>96.533.330-4</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3573,13 +3577,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>3614.32</v>
+        <v>1960.28</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1691-1142-CM25</t>
+          <t>3950-3482-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3599,17 +3603,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3619,12 +3623,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3634,13 +3638,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1960.28</v>
+        <v>770.78</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3950-3482-CM25</t>
+          <t>1691-1043-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3660,17 +3664,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3680,12 +3684,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>HEMISFERIO SUR S.A.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.533.330-4</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3695,7 +3699,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>770.78</v>
+        <v>3614.32</v>
       </c>
     </row>
     <row r="53">
@@ -4819,7 +4823,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2151-194-CM25</t>
+          <t>2151-189-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4859,32 +4863,28 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>745.6799999999999</v>
+        <v>774.78</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2151-189-CM25</t>
+          <t>2151-194-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4924,22 +4924,26 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>774.78</v>
+        <v>745.6799999999999</v>
       </c>
     </row>
     <row r="73">
@@ -5571,7 +5575,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3949-236-CM25</t>
+          <t>1691-1545-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5596,12 +5600,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.974.500-0</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5611,12 +5615,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>COMERCIAL EXPRESS DENT LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>78.378.160-3</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5626,13 +5630,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>3173.63</v>
+        <v>1433.21</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1691-1545-CM25</t>
+          <t>1691-1628-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5687,13 +5691,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1433.21</v>
+        <v>1674.97</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1691-1628-CM25</t>
+          <t>1691-1827-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5733,28 +5737,32 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1674.97</v>
+        <v>5253.66</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1691-1827-CM25</t>
+          <t>418-2049-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5779,12 +5787,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5794,32 +5802,28 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>5253.66</v>
+        <v>1175.31</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>418-2049-CM25</t>
+          <t>3949-236-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5844,12 +5848,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.974.500-0</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>CONSULTORIO GENERAL URBANO DR ALEJANDRO GUTIERREZ</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5859,12 +5863,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>COMERCIAL EXPRESS DENT LIMITADA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>78.378.160-3</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5874,7 +5878,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1175.31</v>
+        <v>3173.63</v>
       </c>
     </row>
     <row r="88">
@@ -6185,7 +6189,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5019-2098-CM25</t>
+          <t>1691-1961-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6210,12 +6214,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>65.224.300-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6225,12 +6229,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>NOVOSALUD SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>76.768.780-k</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6240,13 +6244,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>913.64</v>
+        <v>2602.15</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>418-2319-CM25</t>
+          <t>5019-2098-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6271,12 +6275,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>65.224.300-2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6286,12 +6290,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>NOVOSALUD SPA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.768.780-k</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6301,13 +6305,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2739.35</v>
+        <v>913.64</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1691-1961-CM25</t>
+          <t>418-2319-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6332,12 +6336,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6347,12 +6351,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6362,7 +6366,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>2602.15</v>
+        <v>2739.35</v>
       </c>
     </row>
     <row r="96">
@@ -7051,7 +7055,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1691-2384-CM25</t>
+          <t>1691-2385-CM25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7091,12 +7095,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -7106,7 +7110,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1391.35</v>
+        <v>2432.51</v>
       </c>
     </row>
     <row r="108">
@@ -7173,7 +7177,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1691-2385-CM25</t>
+          <t>1691-2384-CM25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7213,12 +7217,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7228,13 +7232,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>2432.51</v>
+        <v>1391.35</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>418-2690-CM25</t>
+          <t>418-2688-CM25</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7274,12 +7278,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7289,13 +7293,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>2191.18</v>
+        <v>1322.29</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>418-2688-CM25</t>
+          <t>418-2690-CM25</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7335,12 +7339,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7350,13 +7354,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>1322.29</v>
+        <v>2191.18</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>418-2639-CM25</t>
+          <t>1691-2358-CM25</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7381,12 +7385,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7396,12 +7400,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>77.237.150-0</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7411,13 +7415,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>3614.24</v>
+        <v>9763.549999999999</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1691-2358-CM25</t>
+          <t>418-2639-CM25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7442,12 +7446,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7457,12 +7461,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>77.237.150-0</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7472,7 +7476,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>9763.549999999999</v>
+        <v>3614.24</v>
       </c>
     </row>
     <row r="114">
@@ -7860,7 +7864,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1274667-459-CM25</t>
+          <t>1274667-458-CM25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7900,12 +7904,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>COMERCIAL LIMAX SPA</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>76.719.400-5</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7915,13 +7919,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>3199.66</v>
+        <v>897.49</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1274667-458-CM25</t>
+          <t>1274667-459-CM25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7961,12 +7965,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>COMERCIAL LIMAX SPA</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>76.719.400-5</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7976,7 +7980,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>897.49</v>
+        <v>3199.66</v>
       </c>
     </row>
     <row r="122">
@@ -8047,7 +8051,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>418-2980-CM25</t>
+          <t>1691-2500-CM25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8072,12 +8076,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8087,12 +8091,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -8102,13 +8106,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>3670.08</v>
+        <v>1285.03</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1691-2500-CM25</t>
+          <t>418-2980-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8133,12 +8137,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8148,12 +8152,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8163,7 +8167,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>1285.03</v>
+        <v>3670.08</v>
       </c>
     </row>
     <row r="125">
@@ -8339,7 +8343,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8738,7 +8746,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1691-2926-CM25</t>
+          <t>1691-2832-CM25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8778,32 +8786,28 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>5420.72</v>
+        <v>861.02</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1691-2832-CM25</t>
+          <t>1691-2926-CM25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8843,22 +8847,26 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr"/>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>861.02</v>
+        <v>5420.72</v>
       </c>
     </row>
     <row r="136">
@@ -8929,7 +8937,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>418-3376-CM25</t>
+          <t>1691-2651-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8954,12 +8962,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8984,13 +8992,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>1885.98</v>
+        <v>1104.9</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>418-3377-CM25</t>
+          <t>418-3376-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9045,13 +9053,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>750.97</v>
+        <v>1885.98</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1691-2651-CM25</t>
+          <t>418-3377-CM25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9076,12 +9084,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9106,13 +9114,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>1104.9</v>
+        <v>750.97</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>854-343-CM25</t>
+          <t>1691-3004-CM25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9137,12 +9145,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9171,13 +9179,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>740.0700000000001</v>
+        <v>1424.41</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1691-3004-CM25</t>
+          <t>854-343-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9202,12 +9210,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9236,7 +9244,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>1424.41</v>
+        <v>740.0700000000001</v>
       </c>
     </row>
     <row r="142">
@@ -9620,7 +9628,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1691-3117-CM25</t>
+          <t>4609-534-CM25</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9645,12 +9653,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.240.400-9</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9660,28 +9668,32 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>77.237.150-0</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>15314.08</v>
+        <v>2441.6</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>4609-534-CM25</t>
+          <t>1692-2967-CM25</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9706,12 +9718,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9721,32 +9733,28 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.215.260-6</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>2441.6</v>
+        <v>1010.33</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1692-2967-CM25</t>
+          <t>1691-3117-CM25</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9771,12 +9779,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9786,12 +9794,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>77.237.150-0</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9801,7 +9809,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>1010.33</v>
+        <v>15314.08</v>
       </c>
     </row>
     <row r="151">
@@ -10177,7 +10185,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1691-3032-CM25</t>
+          <t>1691-3036-CM25</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10217,32 +10225,28 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>8429.42</v>
+        <v>3964.38</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1691-3036-CM25</t>
+          <t>1691-3176-CM25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10282,12 +10286,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>COMERCIAL LIMAX SPA</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.719.400-5</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10297,13 +10301,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>3964.38</v>
+        <v>3390.85</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1691-3176-CM25</t>
+          <t>2151-432-CM25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10328,12 +10332,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10343,12 +10347,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>COMERCIAL LIMAX SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>76.719.400-5</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -10358,13 +10362,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>3390.85</v>
+        <v>830.51</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2151-432-CM25</t>
+          <t>1691-3032-CM25</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10389,12 +10393,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10404,22 +10408,26 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr"/>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>830.51</v>
+        <v>8429.42</v>
       </c>
     </row>
     <row r="161">
@@ -10799,7 +10807,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1691-3643-CM25</t>
+          <t>1691-3521-CM25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10839,32 +10847,28 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>831.5700000000001</v>
+        <v>4324.38</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1691-3521-CM25</t>
+          <t>1691-3643-CM25</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10904,22 +10908,26 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr"/>
+          <t>96.756.540-7</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>4324.38</v>
+        <v>831.5700000000001</v>
       </c>
     </row>
     <row r="169">
@@ -11173,7 +11181,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1691-3560-CM25</t>
+          <t>1691-3655-CM25</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11213,12 +11221,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
@@ -11228,13 +11236,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>1741.38</v>
+        <v>2656.34</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1691-3655-CM25</t>
+          <t>1691-3560-CM25</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11274,12 +11282,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
@@ -11289,13 +11297,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>2656.34</v>
+        <v>1741.38</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>3950-95-CM26</t>
+          <t>3950-98-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11335,12 +11343,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Jocelyn</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>76.226.228-2</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -11350,13 +11358,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>825.21</v>
+        <v>1978.37</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>3950-98-CM26</t>
+          <t>3950-95-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11396,12 +11404,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>Jocelyn</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.226.228-2</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
@@ -11411,7 +11419,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>1978.37</v>
+        <v>825.21</v>
       </c>
     </row>
     <row r="177">
@@ -11604,7 +11612,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>418-146-CM26</t>
+          <t>418-207-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11663,13 +11671,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>1950.53</v>
+        <v>8092.92</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>418-207-CM26</t>
+          <t>418-146-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11728,7 +11736,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>8092.92</v>
+        <v>1950.53</v>
       </c>
     </row>
     <row r="182">
@@ -12616,7 +12624,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1274667-135-CM26</t>
+          <t>1691-347-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12641,12 +12649,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12656,32 +12664,28 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>4122.52</v>
+        <v>904.5700000000001</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1691-622-CM26</t>
+          <t>418-992-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12706,12 +12710,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12721,12 +12725,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>EXXIMMED 2000 SPA</t>
+          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>78.060.400-k</t>
+          <t>77.237.150-0</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
@@ -12736,13 +12740,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>4311.13</v>
+        <v>785.24</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1691-619-CM26</t>
+          <t>418-1001-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12767,12 +12771,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12782,22 +12786,26 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr"/>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>3850.3</v>
+        <v>1416.51</v>
       </c>
     </row>
     <row r="199">
@@ -12864,7 +12872,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>418-1001-CM26</t>
+          <t>1691-622-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12889,12 +12897,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12904,32 +12912,28 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>EXXIMMED 2000 SPA</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
-        </is>
-      </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.060.400-k</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>1416.51</v>
+        <v>4311.13</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>418-992-CM26</t>
+          <t>1274667-135-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12954,12 +12958,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12969,28 +12973,32 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>77.237.150-0</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>785.24</v>
+        <v>4122.52</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1691-347-CM26</t>
+          <t>1691-619-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -13045,7 +13053,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>904.5700000000001</v>
+        <v>3850.3</v>
       </c>
     </row>
     <row r="203">
@@ -13681,7 +13689,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>418-1268-CM26</t>
+          <t>886182-129-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13706,12 +13714,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13721,28 +13729,32 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
-        </is>
-      </c>
-      <c r="K213" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>1936.96</v>
+        <v>4119.54</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>886182-129-CM26</t>
+          <t>418-1268-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13767,12 +13779,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13782,32 +13794,28 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
-        </is>
-      </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>4119.54</v>
+        <v>1936.96</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1274667-144-CM26</t>
+          <t>886182-131-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13832,12 +13840,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13847,28 +13855,32 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>77.025.316-0</t>
-        </is>
-      </c>
-      <c r="K215" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>1356.69</v>
+        <v>833.3</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>886182-131-CM26</t>
+          <t>1274667-144-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13893,12 +13905,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE AYSEN</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13908,26 +13920,22 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
-        </is>
-      </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.025.316-0</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>833.3</v>
+        <v>1356.69</v>
       </c>
     </row>
     <row r="217">
@@ -14059,7 +14067,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2151-132-CM26</t>
+          <t>1691-795-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14084,12 +14092,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -14099,28 +14107,32 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>77.025.316-0</t>
-        </is>
-      </c>
-      <c r="K219" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>1462.89</v>
+        <v>1827.23</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>418-1223-CM26</t>
+          <t>2151-132-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -14145,12 +14157,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -14160,12 +14172,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>77.025.316-0</t>
         </is>
       </c>
       <c r="K220" t="inlineStr"/>
@@ -14175,13 +14187,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>1181.13</v>
+        <v>1462.89</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1691-795-CM26</t>
+          <t>418-1223-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14206,12 +14218,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14221,12 +14233,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
@@ -14236,7 +14248,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>1827.23</v>
+        <v>1181.13</v>
       </c>
     </row>
     <row r="222">
@@ -14307,7 +14319,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1691-824-CM26</t>
+          <t>1691-856-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14347,28 +14359,32 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
-        </is>
-      </c>
-      <c r="K223" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>4802.76</v>
+        <v>825.29</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1691-856-CM26</t>
+          <t>1691-824-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14408,26 +14424,22 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>825.29</v>
+        <v>4802.76</v>
       </c>
     </row>
     <row r="225">
@@ -14498,7 +14510,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1691-797-CM26</t>
+          <t>1691-938-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14538,12 +14550,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>CONVATEC CHILE S.A.</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.020.266-5</t>
         </is>
       </c>
       <c r="K226" t="inlineStr"/>
@@ -14553,13 +14565,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>10400.82</v>
+        <v>1824.59</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1691-799-CM26</t>
+          <t>1691-837-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14599,28 +14611,32 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>HEMISFERIO SUR S.A.</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>96.533.330-4</t>
-        </is>
-      </c>
-      <c r="K227" t="inlineStr"/>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>4870.2</v>
+        <v>17577.5</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1691-837-CM26</t>
+          <t>1691-799-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14660,32 +14676,28 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>HEMISFERIO SUR S.A.</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
-        </is>
-      </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.533.330-4</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr"/>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>17577.5</v>
+        <v>4870.2</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1691-938-CM26</t>
+          <t>1691-797-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14725,12 +14737,12 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>CONVATEC CHILE S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>76.020.266-5</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
@@ -14740,13 +14752,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>1824.59</v>
+        <v>10400.82</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1691-866-CM26</t>
+          <t>1691-865-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14786,28 +14798,32 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>HEMISFERIO SUR S.A.</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>96.533.330-4</t>
-        </is>
-      </c>
-      <c r="K230" t="inlineStr"/>
+          <t>96.756.540-7</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>2847.14</v>
+        <v>8623.559999999999</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1691-865-CM26</t>
+          <t>1691-866-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14847,32 +14863,28 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>HEMISFERIO SUR S.A.</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
-        </is>
-      </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.533.330-4</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr"/>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>8623.559999999999</v>
+        <v>2847.14</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1691-941-CM26</t>
+          <t>418-1502-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14897,12 +14909,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14912,12 +14924,12 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>CLINICON SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>77.070.635-1</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K232" t="inlineStr"/>
@@ -14927,13 +14939,13 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>10158.79</v>
+        <v>878.52</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>418-1502-CM26</t>
+          <t>1691-977-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -14958,12 +14970,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14973,12 +14985,12 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K233" t="inlineStr"/>
@@ -14988,13 +15000,13 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>878.52</v>
+        <v>952.54</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1691-977-CM26</t>
+          <t>1691-941-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -15034,12 +15046,12 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>CLINICON SPA</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>77.070.635-1</t>
         </is>
       </c>
       <c r="K234" t="inlineStr"/>
@@ -15049,13 +15061,13 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>952.54</v>
+        <v>10158.79</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1691-923-CM26</t>
+          <t>1691-992-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15095,12 +15107,12 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K235" t="inlineStr"/>
@@ -15110,13 +15122,13 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>3347.83</v>
+        <v>5395.51</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>3765-399-CM26</t>
+          <t>1691-923-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15141,7 +15153,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -15156,32 +15168,28 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
-        </is>
-      </c>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr"/>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>932.53</v>
+        <v>3347.83</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1691-982-CM26</t>
+          <t>1691-994-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15221,12 +15229,12 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K237" t="inlineStr"/>
@@ -15236,13 +15244,13 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>3978.09</v>
+        <v>1721.64</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1691-992-CM26</t>
+          <t>1691-982-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15282,12 +15290,12 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K238" t="inlineStr"/>
@@ -15297,13 +15305,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>5395.51</v>
+        <v>3978.09</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1691-994-CM26</t>
+          <t>3765-399-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15328,7 +15336,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -15343,22 +15351,26 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
-        </is>
-      </c>
-      <c r="K239" t="inlineStr"/>
+          <t>96.756.540-7</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>1721.64</v>
+        <v>932.53</v>
       </c>
     </row>
     <row r="240">
@@ -15473,7 +15485,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15486,7 +15502,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1691-704-CM26</t>
+          <t>1691-1082-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15526,22 +15542,26 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
-        </is>
-      </c>
-      <c r="K242" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>4382.72</v>
+        <v>15585.27</v>
       </c>
     </row>
     <row r="243">
@@ -15612,7 +15632,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1691-1082-CM26</t>
+          <t>1691-704-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15652,12 +15672,12 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K244" t="inlineStr"/>
@@ -15667,7 +15687,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>15585.27</v>
+        <v>4382.72</v>
       </c>
     </row>
     <row r="245">
@@ -15864,7 +15884,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1691-743-CM26</t>
+          <t>1691-1038-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15923,13 +15943,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>4262.29</v>
+        <v>1773.73</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1691-1038-CM26</t>
+          <t>1691-743-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -15988,7 +16008,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>1773.73</v>
+        <v>4262.29</v>
       </c>
     </row>
     <row r="250">
@@ -16181,7 +16201,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1691-1101-CM26</t>
+          <t>1691-1103-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -16221,32 +16241,28 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>PTM Emergencia</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
-        </is>
-      </c>
-      <c r="K253" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.612.187-K</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>2084.21</v>
+        <v>4196.86</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1691-1103-CM26</t>
+          <t>1691-1101-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -16286,28 +16302,32 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>PTM Emergencia</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>76.612.187-K</t>
-        </is>
-      </c>
-      <c r="K254" t="inlineStr"/>
+          <t>96.756.540-7</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>4196.86</v>
+        <v>2084.21</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>418-1885-CM26</t>
+          <t>418-1826-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16347,28 +16367,32 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>MEDISAN CHILE SPA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>76.426.475-4</t>
-        </is>
-      </c>
-      <c r="K255" t="inlineStr"/>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>869.55</v>
+        <v>1112.41</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>418-1884-CM26</t>
+          <t>418-1882-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16408,12 +16432,12 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -16427,13 +16451,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>1596.03</v>
+        <v>814.73</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>418-1882-CM26</t>
+          <t>418-1844-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16492,13 +16516,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>814.73</v>
+        <v>792.36</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>418-1886-CM26</t>
+          <t>418-1831-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16538,12 +16562,12 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K258" t="inlineStr"/>
@@ -16553,13 +16577,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>923.35</v>
+        <v>826.9</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>418-1831-CM26</t>
+          <t>418-1825-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16599,12 +16623,12 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K259" t="inlineStr"/>
@@ -16614,13 +16638,13 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>826.9</v>
+        <v>1947.45</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>418-1826-CM26</t>
+          <t>418-1886-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16660,32 +16684,28 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.190.880-2</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>1112.41</v>
+        <v>923.35</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>418-1825-CM26</t>
+          <t>418-1884-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16725,28 +16745,32 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
-        </is>
-      </c>
-      <c r="K261" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>1947.45</v>
+        <v>1596.03</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>418-1844-CM26</t>
+          <t>418-1885-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16786,26 +16810,22 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>MEDISAN CHILE SPA</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.426.475-4</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr"/>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>792.36</v>
+        <v>869.55</v>
       </c>
     </row>
     <row r="263">
@@ -17242,7 +17262,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1691-1275-CM26</t>
+          <t>1691-1222-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17282,12 +17302,12 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>CONVATEC CHILE S.A.</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>76.020.266-5</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K270" t="inlineStr"/>
@@ -17297,13 +17317,13 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>12575.64</v>
+        <v>1140.02</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1692-423-CM26</t>
+          <t>1691-1272-CM26</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -17328,12 +17348,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -17343,28 +17363,32 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
-        </is>
-      </c>
-      <c r="K271" t="inlineStr"/>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>797.8200000000001</v>
+        <v>29342.18</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1691-1222-CM26</t>
+          <t>1691-1275-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17404,12 +17428,12 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>CONVATEC CHILE S.A.</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>76.020.266-5</t>
         </is>
       </c>
       <c r="K272" t="inlineStr"/>
@@ -17419,13 +17443,13 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>1140.02</v>
+        <v>12575.64</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>1691-1272-CM26</t>
+          <t>1692-423-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17450,12 +17474,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -17465,26 +17489,22 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K273" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.190.880-2</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>29342.18</v>
+        <v>797.8200000000001</v>
       </c>
     </row>
     <row r="274">
@@ -17538,7 +17558,11 @@
           <t>84.609.600-0</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17612,7 +17636,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>707426-103-CM26</t>
+          <t>1692-451-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -17637,12 +17661,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -17652,12 +17676,12 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>DIFEM LABORATORIOS S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>79.581.120-6</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K276" t="inlineStr"/>
@@ -17667,13 +17691,13 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>811.54</v>
+        <v>1147.05</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>1692-451-CM26</t>
+          <t>707426-105-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -17698,12 +17722,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -17713,28 +17737,32 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
-        </is>
-      </c>
-      <c r="K277" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>1147.05</v>
+        <v>1859.37</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>707426-105-CM26</t>
+          <t>707426-103-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -17774,26 +17802,22 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>DIFEM LABORATORIOS S A</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
-        </is>
-      </c>
-      <c r="K278" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.581.120-6</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>1859.37</v>
+        <v>811.54</v>
       </c>
     </row>
     <row r="279">
@@ -17847,7 +17871,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17860,7 +17888,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1691-1414-CM26</t>
+          <t>1691-1286-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -17900,26 +17928,22 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
-        </is>
-      </c>
-      <c r="K280" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr"/>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>19134.3</v>
+        <v>8466.65</v>
       </c>
     </row>
     <row r="281">
@@ -17986,7 +18010,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1691-1271-CM26</t>
+          <t>1691-1414-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18026,28 +18050,32 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
-        </is>
-      </c>
-      <c r="K282" t="inlineStr"/>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>2036.47</v>
+        <v>19134.3</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>1691-1286-CM26</t>
+          <t>1691-1271-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18087,12 +18115,12 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K283" t="inlineStr"/>
@@ -18102,7 +18130,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>8466.65</v>
+        <v>2036.47</v>
       </c>
     </row>
     <row r="284">
@@ -18299,7 +18327,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>418-2228-CM26</t>
+          <t>418-2237-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -18339,28 +18367,32 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
-        </is>
-      </c>
-      <c r="K287" t="inlineStr"/>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>1188.06</v>
+        <v>1066.43</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>418-2237-CM26</t>
+          <t>3950-1038-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -18380,17 +18412,17 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -18400,12 +18432,12 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -18419,13 +18451,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>1066.43</v>
+        <v>11688.91</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>3950-1038-CM26</t>
+          <t>418-2228-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -18445,17 +18477,17 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -18465,26 +18497,22 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
-        </is>
-      </c>
-      <c r="K289" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr"/>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>11688.91</v>
+        <v>1188.06</v>
       </c>
     </row>
     <row r="290">
@@ -18612,7 +18640,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>418-2305-CM26</t>
+          <t>418-2297-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -18652,12 +18680,12 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>IMPORTADORA MEGA MARKET LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>76.012.551-2</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K292" t="inlineStr"/>
@@ -18667,13 +18695,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>1337.42</v>
+        <v>1555.13</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>418-2297-CM26</t>
+          <t>418-2305-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -18713,12 +18741,12 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>IMPORTADORA MEGA MARKET LIMITADA</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.012.551-2</t>
         </is>
       </c>
       <c r="K293" t="inlineStr"/>
@@ -18728,13 +18756,13 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>1555.13</v>
+        <v>1337.42</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1691-1527-CM26</t>
+          <t>1691-1587-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -18754,7 +18782,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -18774,12 +18802,12 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>Medisan Limitada</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>77.693.540-9</t>
         </is>
       </c>
       <c r="K294" t="inlineStr"/>
@@ -18789,13 +18817,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>3352.08</v>
+        <v>1197.19</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>1691-1587-CM26</t>
+          <t>1691-1527-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -18815,7 +18843,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -18835,12 +18863,12 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>Medisan Limitada</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>77.693.540-9</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K295" t="inlineStr"/>
@@ -18850,7 +18878,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>1197.19</v>
+        <v>3352.08</v>
       </c>
     </row>
     <row r="296">
@@ -18978,7 +19006,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>418-2473-CM26</t>
+          <t>3765-672-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19003,12 +19031,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -19018,28 +19046,32 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>77.237.150-0</t>
-        </is>
-      </c>
-      <c r="K298" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>807.11</v>
+        <v>925.6799999999999</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>418-2482-CM26</t>
+          <t>418-2473-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19079,12 +19111,12 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>77.237.150-0</t>
         </is>
       </c>
       <c r="K299" t="inlineStr"/>
@@ -19094,13 +19126,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>818.3</v>
+        <v>807.11</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>3765-672-CM26</t>
+          <t>418-2482-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19125,12 +19157,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -19140,26 +19172,22 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
-        </is>
-      </c>
-      <c r="K300" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.215.260-6</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr"/>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>925.6799999999999</v>
+        <v>818.3</v>
       </c>
     </row>
     <row r="301">
@@ -19413,7 +19441,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2151-318-CM26</t>
+          <t>2151-324-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -19453,12 +19481,12 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
@@ -19472,7 +19500,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>1295.9</v>
+        <v>861.02</v>
       </c>
     </row>
     <row r="306">
@@ -19539,7 +19567,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2151-320-CM26</t>
+          <t>2151-318-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -19579,28 +19607,32 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>DELTAMED LIMITADA</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>76.512.686-k</t>
-        </is>
-      </c>
-      <c r="K307" t="inlineStr"/>
+          <t>96.756.540-7</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>1843.42</v>
+        <v>1295.9</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2151-324-CM26</t>
+          <t>2151-320-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -19640,26 +19672,22 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>DELTAMED LIMITADA</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
-        </is>
-      </c>
-      <c r="K308" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.512.686-k</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr"/>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>861.02</v>
+        <v>1843.42</v>
       </c>
     </row>
     <row r="309">
@@ -19713,7 +19741,11 @@
           <t>84.609.600-0</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19726,7 +19758,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>1692-574-CM26</t>
+          <t>1692-576-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -19766,12 +19798,12 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K310" t="inlineStr"/>
@@ -19781,13 +19813,13 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>823.88</v>
+        <v>824.14</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>1692-576-CM26</t>
+          <t>1692-574-CM26</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -19827,12 +19859,12 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K311" t="inlineStr"/>
@@ -19842,7 +19874,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>824.14</v>
+        <v>823.88</v>
       </c>
     </row>
     <row r="312">
@@ -19913,7 +19945,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>1274667-329-CM26</t>
+          <t>1691-1792-CM26</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -19938,12 +19970,12 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -19953,26 +19985,22 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
-        </is>
-      </c>
-      <c r="K313" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr"/>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>4906.29</v>
+        <v>3171.65</v>
       </c>
     </row>
     <row r="314">
@@ -20043,7 +20071,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>1691-1792-CM26</t>
+          <t>1274667-329-CM26</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -20068,12 +20096,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -20083,28 +20111,32 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
-        </is>
-      </c>
-      <c r="K315" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>3171.65</v>
+        <v>4906.29</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>1691-1736-CM26</t>
+          <t>1691-1738-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -20144,12 +20176,12 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>CONVATEC CHILE S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>76.020.266-5</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K316" t="inlineStr"/>
@@ -20159,13 +20191,13 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>1299.9</v>
+        <v>2366.71</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>1691-1738-CM26</t>
+          <t>1691-1736-CM26</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -20205,12 +20237,12 @@
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>CONVATEC CHILE S.A.</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.020.266-5</t>
         </is>
       </c>
       <c r="K317" t="inlineStr"/>
@@ -20220,7 +20252,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>2366.71</v>
+        <v>1299.9</v>
       </c>
     </row>
     <row r="318">
@@ -20665,7 +20697,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>1692-643-CM26</t>
+          <t>1692-644-CM26</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -20685,7 +20717,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
@@ -20705,12 +20737,12 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K325" t="inlineStr"/>
@@ -20720,13 +20752,13 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>1040.73</v>
+        <v>766.34</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>1692-644-CM26</t>
+          <t>1692-643-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -20766,12 +20798,12 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K326" t="inlineStr"/>
@@ -20781,7 +20813,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>766.34</v>
+        <v>1040.73</v>
       </c>
     </row>
     <row r="327">
@@ -20848,7 +20880,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>1691-1923-CM26</t>
+          <t>1274667-356-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -20873,12 +20905,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -20888,28 +20920,32 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>CLINICON SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>77.070.635-1</t>
-        </is>
-      </c>
-      <c r="K328" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>5355</v>
+        <v>2797.5</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>1274667-356-CM26</t>
+          <t>1691-1923-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -20934,12 +20970,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -20949,26 +20985,22 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>CLINICON SPA</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
-        </is>
-      </c>
-      <c r="K329" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.070.635-1</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr"/>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>2797.5</v>
+        <v>5355</v>
       </c>
     </row>
     <row r="330">
@@ -21039,7 +21071,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>418-3059-CM26</t>
+          <t>418-3097-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -21079,12 +21111,12 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>MEDISAN CHILE SPA</t>
+          <t>MEDIPLEX S A</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>76.426.475-4</t>
+          <t>86.383.300-0</t>
         </is>
       </c>
       <c r="K331" t="inlineStr"/>
@@ -21094,13 +21126,13 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>830.2</v>
+        <v>940.38</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>1691-1774-CM26</t>
+          <t>418-3059-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -21125,12 +21157,12 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -21140,32 +21172,28 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>MEDISAN CHILE SPA</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K332" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.426.475-4</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr"/>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>1395.42</v>
+        <v>830.2</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>418-3097-CM26</t>
+          <t>1691-1774-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -21190,12 +21218,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -21205,28 +21233,32 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>MEDIPLEX S A</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>86.383.300-0</t>
-        </is>
-      </c>
-      <c r="K333" t="inlineStr"/>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>940.38</v>
+        <v>1395.42</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>1691-2057-CM26</t>
+          <t>1691-1921-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -21285,68 +21317,950 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>15236.34</v>
+        <v>3444.35</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
+          <t>1691-2057-CM26</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M335" s="2" t="n">
+        <v>15236.34</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
           <t>418-3235-CM26</t>
         </is>
       </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>2239-21-LR23</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr">
+      <c r="D336" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="E335" t="inlineStr">
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>61.602.279-2</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>TECNIKA S A</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr"/>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M336" s="2" t="n">
+        <v>1556.5</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>1691-1919-CM26</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr"/>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M337" s="2" t="n">
+        <v>3210.57</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>1691-2014-CM26</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M338" s="2" t="n">
+        <v>1261.15</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>418-3274-CM26</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>61.602.279-2</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>TECNIKA S A</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr"/>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M339" s="2" t="n">
+        <v>1005.34</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>1691-2083-CM26</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M340" s="2" t="n">
+        <v>4978.37</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>1691-2086-CM26</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>CLINICON SPA</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>77.070.635-1</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr"/>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M341" s="2" t="n">
+        <v>2178.02</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>734-715-CM26</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>61.607.800-3</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>B BRAUN MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>96.756.540-7</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M342" s="2" t="n">
+        <v>1572.54</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>3950-1606-CM26</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F335" t="inlineStr">
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>61.974.600-7</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>DIRECCION SALUD RURAL</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>REUTTER S A</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M343" s="2" t="n">
+        <v>5259.91</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>3950-1607-CM26</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>61.974.600-7</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>DIRECCION SALUD RURAL</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>NEMO CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>76.215.260-6</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr"/>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M344" s="2" t="n">
+        <v>1071.98</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>418-3436-CM26</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
         <is>
           <t>61.602.279-2</t>
         </is>
       </c>
-      <c r="G335" t="inlineStr">
+      <c r="G345" t="inlineStr">
         <is>
           <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
-      <c r="H335" t="inlineStr">
-        <is>
-          <t>Aysén</t>
-        </is>
-      </c>
-      <c r="I335" t="inlineStr">
-        <is>
-          <t>TECNIKA S A</t>
-        </is>
-      </c>
-      <c r="J335" t="inlineStr">
-        <is>
-          <t>96.625.950-7</t>
-        </is>
-      </c>
-      <c r="K335" t="inlineStr"/>
-      <c r="L335" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M335" s="2" t="n">
-        <v>1556.5</v>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>IMPORTADORA MEGA MARKET LIMITADA</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>76.012.551-2</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr"/>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M345" s="2" t="n">
+        <v>1272.28</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>418-3510-CM26</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>61.602.279-2</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>IMPORTADORA MEGA MARKET LIMITADA</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>76.012.551-2</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr"/>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M346" s="2" t="n">
+        <v>1275.44</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>1691-2182-CM26</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>REUTTER S A</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M347" s="2" t="n">
+        <v>2242.34</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>1691-2188-CM26</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M348" s="2" t="n">
+        <v>973.01</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>418-3579-CM26</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>61.602.279-2</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>MEDISAN CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>76.426.475-4</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr"/>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M349" s="2" t="n">
+        <v>807.3200000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/insumos-y-dispositivos-medicos/aysen.xlsx
+++ b/docs/oc-regiones/insumos-y-dispositivos-medicos/aysen.xlsx
@@ -18843,7 +18843,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">

--- a/docs/oc-regiones/insumos-y-dispositivos-medicos/aysen.xlsx
+++ b/docs/oc-regiones/insumos-y-dispositivos-medicos/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M349"/>
+  <dimension ref="A1:M351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4823,7 +4823,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2151-189-CM25</t>
+          <t>2151-194-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4863,28 +4863,32 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>774.78</v>
+        <v>745.6799999999999</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2151-194-CM25</t>
+          <t>2151-189-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4924,26 +4928,22 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>745.6799999999999</v>
+        <v>774.78</v>
       </c>
     </row>
     <row r="73">
@@ -8295,7 +8295,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1691-2627-CM25</t>
+          <t>418-3310-CM25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8320,12 +8320,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -8354,13 +8354,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>2126.54</v>
+        <v>1830.69</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1691-2629-CM25</t>
+          <t>1691-2672-CM25</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8400,12 +8400,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -8419,13 +8419,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>1147.9</v>
+        <v>3586.67</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1691-2672-CM25</t>
+          <t>1691-2629-CM25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8465,12 +8465,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>3586.67</v>
+        <v>1147.9</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>418-3310-CM25</t>
+          <t>1691-2627-CM25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -8549,7 +8549,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>1830.69</v>
+        <v>2126.54</v>
       </c>
     </row>
     <row r="131">
@@ -8746,7 +8746,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1691-2832-CM25</t>
+          <t>1691-2926-CM25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8786,28 +8786,32 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr"/>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>861.02</v>
+        <v>5420.72</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1691-2926-CM25</t>
+          <t>1691-2832-CM25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8847,32 +8851,28 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>5420.72</v>
+        <v>861.02</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1691-2647-CM25</t>
+          <t>418-3377-CM25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8912,32 +8912,28 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1479.81</v>
+        <v>750.97</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1691-2651-CM25</t>
+          <t>418-3376-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8962,12 +8958,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8992,13 +8988,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>1104.9</v>
+        <v>1885.98</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>418-3376-CM25</t>
+          <t>1691-2651-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9023,12 +9019,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9053,13 +9049,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1885.98</v>
+        <v>1104.9</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>418-3377-CM25</t>
+          <t>1691-2647-CM25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9084,12 +9080,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9099,28 +9095,32 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr"/>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>750.97</v>
+        <v>1479.81</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1691-3004-CM25</t>
+          <t>854-343-CM25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9145,12 +9145,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9179,13 +9179,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1424.41</v>
+        <v>740.0700000000001</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>854-343-CM25</t>
+          <t>1691-3004-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9210,12 +9210,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9244,7 +9244,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>740.0700000000001</v>
+        <v>1424.41</v>
       </c>
     </row>
     <row r="142">
@@ -9628,7 +9628,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>4609-534-CM25</t>
+          <t>1691-3117-CM25</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9668,32 +9668,28 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.237.150-0</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>2441.6</v>
+        <v>15314.08</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1692-2967-CM25</t>
+          <t>4609-534-CM25</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9718,12 +9714,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>69.240.400-9</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9733,28 +9729,32 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1010.33</v>
+        <v>2441.6</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1691-3117-CM25</t>
+          <t>1692-2967-CM25</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9779,12 +9779,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>77.237.150-0</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9809,7 +9809,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>15314.08</v>
+        <v>1010.33</v>
       </c>
     </row>
     <row r="151">
@@ -9876,7 +9876,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1691-3192-CM25</t>
+          <t>1691-3191-CM25</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9931,13 +9931,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>2517.21</v>
+        <v>814.08</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1691-3191-CM25</t>
+          <t>1691-3192-CM25</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9992,7 +9992,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>814.08</v>
+        <v>2517.21</v>
       </c>
     </row>
     <row r="154">
@@ -10185,7 +10185,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1691-3036-CM25</t>
+          <t>1691-3032-CM25</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10225,28 +10225,32 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr"/>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>3964.38</v>
+        <v>8429.42</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1691-3176-CM25</t>
+          <t>1691-3036-CM25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10286,12 +10290,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>COMERCIAL LIMAX SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>76.719.400-5</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10301,13 +10305,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>3390.85</v>
+        <v>3964.38</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2151-432-CM25</t>
+          <t>1691-3176-CM25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10332,12 +10336,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10347,12 +10351,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>COMERCIAL LIMAX SPA</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>76.719.400-5</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -10362,13 +10366,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>830.51</v>
+        <v>3390.85</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1691-3032-CM25</t>
+          <t>2151-432-CM25</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10393,12 +10397,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10408,26 +10412,22 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.215.260-6</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>8429.42</v>
+        <v>830.51</v>
       </c>
     </row>
     <row r="161">
@@ -11181,7 +11181,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1691-3655-CM25</t>
+          <t>1691-3560-CM25</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
@@ -11236,13 +11236,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>2656.34</v>
+        <v>1741.38</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1691-3560-CM25</t>
+          <t>1691-3655-CM25</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
@@ -11297,7 +11297,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>1741.38</v>
+        <v>2656.34</v>
       </c>
     </row>
     <row r="175">
@@ -12685,7 +12685,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>418-992-CM26</t>
+          <t>418-1001-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12725,28 +12725,32 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>77.237.150-0</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr"/>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>785.24</v>
+        <v>1416.51</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>418-1001-CM26</t>
+          <t>1691-610-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12771,12 +12775,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12786,32 +12790,28 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>1416.51</v>
+        <v>3390.59</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1691-610-CM26</t>
+          <t>1691-619-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12851,12 +12851,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>3390.59</v>
+        <v>3850.3</v>
       </c>
     </row>
     <row r="200">
@@ -12998,7 +12998,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1691-619-CM26</t>
+          <t>418-992-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -13023,12 +13023,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>77.237.150-0</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
@@ -13053,7 +13053,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>3850.3</v>
+        <v>785.24</v>
       </c>
     </row>
     <row r="203">
@@ -13815,7 +13815,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>886182-131-CM26</t>
+          <t>1274667-144-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13840,12 +13840,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE AYSEN</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13855,32 +13855,28 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
-        </is>
-      </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.025.316-0</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>833.3</v>
+        <v>1356.69</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1274667-144-CM26</t>
+          <t>886182-131-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13905,12 +13901,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13920,28 +13916,32 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>77.025.316-0</t>
-        </is>
-      </c>
-      <c r="K216" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>1356.69</v>
+        <v>833.3</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1691-808-CM26</t>
+          <t>1691-795-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>29913.86</v>
+        <v>1827.23</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>734-240-CM26</t>
+          <t>418-1223-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14031,12 +14031,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -14046,12 +14046,12 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>77.190.880-2</t>
         </is>
       </c>
       <c r="K218" t="inlineStr"/>
@@ -14061,13 +14061,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>8284.610000000001</v>
+        <v>1181.13</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1691-795-CM26</t>
+          <t>1691-808-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14107,12 +14107,12 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -14126,7 +14126,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>1827.23</v>
+        <v>29913.86</v>
       </c>
     </row>
     <row r="220">
@@ -14193,7 +14193,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>418-1223-CM26</t>
+          <t>734-240-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14218,12 +14218,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14233,12 +14233,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
@@ -14248,7 +14248,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>1181.13</v>
+        <v>8284.610000000001</v>
       </c>
     </row>
     <row r="222">
@@ -14319,7 +14319,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1691-856-CM26</t>
+          <t>1691-857-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14359,12 +14359,12 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>96.756.540-7</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -14378,13 +14378,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>825.29</v>
+        <v>2637.63</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1691-824-CM26</t>
+          <t>1691-856-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14424,28 +14424,32 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
-        </is>
-      </c>
-      <c r="K224" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>4802.76</v>
+        <v>825.29</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1691-857-CM26</t>
+          <t>1691-824-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14485,26 +14489,22 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
-        </is>
-      </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>2637.63</v>
+        <v>4802.76</v>
       </c>
     </row>
     <row r="226">
@@ -15067,7 +15067,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1691-992-CM26</t>
+          <t>1691-923-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15107,12 +15107,12 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K235" t="inlineStr"/>
@@ -15122,13 +15122,13 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>5395.51</v>
+        <v>3347.83</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1691-923-CM26</t>
+          <t>3765-399-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15153,7 +15153,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -15168,28 +15168,32 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
-        </is>
-      </c>
-      <c r="K236" t="inlineStr"/>
+          <t>96.756.540-7</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>3347.83</v>
+        <v>932.53</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1691-994-CM26</t>
+          <t>1691-982-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15229,12 +15233,12 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K237" t="inlineStr"/>
@@ -15244,13 +15248,13 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>1721.64</v>
+        <v>3978.09</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1691-982-CM26</t>
+          <t>1691-992-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15290,12 +15294,12 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K238" t="inlineStr"/>
@@ -15305,13 +15309,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>3978.09</v>
+        <v>5395.51</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>3765-399-CM26</t>
+          <t>1691-994-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15336,7 +15340,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -15351,26 +15355,22 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
-        </is>
-      </c>
-      <c r="K239" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr"/>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>932.53</v>
+        <v>1721.64</v>
       </c>
     </row>
     <row r="240">
@@ -15502,7 +15502,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1691-1082-CM26</t>
+          <t>1691-704-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15542,26 +15542,22 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K242" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>80.447.400-5</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr"/>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>15585.27</v>
+        <v>4382.72</v>
       </c>
     </row>
     <row r="243">
@@ -15632,7 +15628,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1691-704-CM26</t>
+          <t>1691-1082-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15672,22 +15668,26 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
-        </is>
-      </c>
-      <c r="K244" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>4382.72</v>
+        <v>15585.27</v>
       </c>
     </row>
     <row r="245">
@@ -16327,7 +16327,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>418-1826-CM26</t>
+          <t>418-1886-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16367,32 +16367,28 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K255" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.190.880-2</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr"/>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>1112.41</v>
+        <v>923.35</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>418-1882-CM26</t>
+          <t>418-1884-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16432,12 +16428,12 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>B BRAUN MEDICAL SPA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>96.756.540-7</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -16451,13 +16447,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>814.73</v>
+        <v>1596.03</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>418-1844-CM26</t>
+          <t>418-1882-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16516,13 +16512,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>792.36</v>
+        <v>814.73</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>418-1831-CM26</t>
+          <t>418-1844-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16562,28 +16558,32 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>B BRAUN MEDICAL SPA</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
-        </is>
-      </c>
-      <c r="K258" t="inlineStr"/>
+          <t>96.756.540-7</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>826.9</v>
+        <v>792.36</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>418-1825-CM26</t>
+          <t>418-1831-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16623,12 +16623,12 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K259" t="inlineStr"/>
@@ -16638,13 +16638,13 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>1947.45</v>
+        <v>826.9</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>418-1886-CM26</t>
+          <t>418-1826-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16684,28 +16684,32 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>SOC IMPORTADORA OPTIVISION LIMITADA</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>77.190.880-2</t>
-        </is>
-      </c>
-      <c r="K260" t="inlineStr"/>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>923.35</v>
+        <v>1112.41</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>418-1884-CM26</t>
+          <t>418-1825-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16745,26 +16749,22 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
-        </is>
-      </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr"/>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>1596.03</v>
+        <v>1947.45</v>
       </c>
     </row>
     <row r="262">
@@ -16953,7 +16953,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1691-1280-CM26</t>
+          <t>2151-222-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -16978,12 +16978,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16993,12 +16993,12 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
+          <t>DELTAMED LIMITADA</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>77.237.150-0</t>
+          <t>76.512.686-k</t>
         </is>
       </c>
       <c r="K265" t="inlineStr"/>
@@ -17008,13 +17008,13 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>16354.64</v>
+        <v>896.66</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2151-222-CM26</t>
+          <t>2151-223-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -17054,12 +17054,12 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>DELTAMED LIMITADA</t>
+          <t>MEDIPLEX S A</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>76.512.686-k</t>
+          <t>86.383.300-0</t>
         </is>
       </c>
       <c r="K266" t="inlineStr"/>
@@ -17069,13 +17069,13 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>896.66</v>
+        <v>1358.53</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2151-223-CM26</t>
+          <t>1691-1280-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17100,12 +17100,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>61.602.293-8</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -17115,12 +17115,12 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>MEDIPLEX S A</t>
+          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>86.383.300-0</t>
+          <t>77.237.150-0</t>
         </is>
       </c>
       <c r="K267" t="inlineStr"/>
@@ -17130,7 +17130,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>1358.53</v>
+        <v>16354.64</v>
       </c>
     </row>
     <row r="268">
@@ -17636,7 +17636,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1692-451-CM26</t>
+          <t>707426-103-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -17661,12 +17661,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -17676,12 +17676,12 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>DIFEM LABORATORIOS S A</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>79.581.120-6</t>
         </is>
       </c>
       <c r="K276" t="inlineStr"/>
@@ -17691,7 +17691,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>1147.05</v>
+        <v>811.54</v>
       </c>
     </row>
     <row r="277">
@@ -17762,7 +17762,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>707426-103-CM26</t>
+          <t>1692-451-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -17787,12 +17787,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -17802,12 +17802,12 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>DIFEM LABORATORIOS S A</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>79.581.120-6</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K278" t="inlineStr"/>
@@ -17817,7 +17817,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>811.54</v>
+        <v>1147.05</v>
       </c>
     </row>
     <row r="279">
@@ -17888,7 +17888,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1691-1286-CM26</t>
+          <t>1691-1414-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -17928,22 +17928,26 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
-        </is>
-      </c>
-      <c r="K280" t="inlineStr"/>
+          <t>93.366.000-1</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>8466.65</v>
+        <v>19134.3</v>
       </c>
     </row>
     <row r="281">
@@ -18010,7 +18014,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1691-1414-CM26</t>
+          <t>1691-1286-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18050,26 +18054,22 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
-        </is>
-      </c>
-      <c r="K282" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr"/>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>19134.3</v>
+        <v>8466.65</v>
       </c>
     </row>
     <row r="283">
@@ -18136,7 +18136,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>418-2221-CM26</t>
+          <t>1691-1479-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18161,12 +18161,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18176,12 +18176,12 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>COMERCIAL LBF LIMITADA</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>93.366.000-1</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -18195,13 +18195,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>2109</v>
+        <v>796.87</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1691-1479-CM26</t>
+          <t>418-2221-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18226,12 +18226,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18241,12 +18241,12 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>COMERCIAL LBF LIMITADA</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>93.366.000-1</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
@@ -18260,7 +18260,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>796.87</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="286">
@@ -18640,7 +18640,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>418-2297-CM26</t>
+          <t>418-2305-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -18680,12 +18680,12 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>IMPORTADORA MEGA MARKET LIMITADA</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>76.012.551-2</t>
         </is>
       </c>
       <c r="K292" t="inlineStr"/>
@@ -18695,13 +18695,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>1555.13</v>
+        <v>1337.42</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>418-2305-CM26</t>
+          <t>418-2297-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -18741,12 +18741,12 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>IMPORTADORA MEGA MARKET LIMITADA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>76.012.551-2</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K293" t="inlineStr"/>
@@ -18756,13 +18756,13 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>1337.42</v>
+        <v>1555.13</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1691-1587-CM26</t>
+          <t>1691-1527-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -18802,12 +18802,12 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>Medisan Limitada</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>77.693.540-9</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K294" t="inlineStr"/>
@@ -18817,13 +18817,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>1197.19</v>
+        <v>3352.08</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>1691-1527-CM26</t>
+          <t>1691-1587-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -18863,12 +18863,12 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
+          <t>Medisan Limitada</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>78.566.250-4</t>
+          <t>77.693.540-9</t>
         </is>
       </c>
       <c r="K295" t="inlineStr"/>
@@ -18878,7 +18878,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>3352.08</v>
+        <v>1197.19</v>
       </c>
     </row>
     <row r="296">
@@ -19006,7 +19006,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>3765-672-CM26</t>
+          <t>418-2473-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19031,12 +19031,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>61.602.281-4</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -19046,32 +19046,28 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
-        </is>
-      </c>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.237.150-0</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr"/>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>925.6799999999999</v>
+        <v>807.11</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>418-2473-CM26</t>
+          <t>418-2482-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19111,12 +19107,12 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>77.237.150-0</t>
+          <t>76.215.260-6</t>
         </is>
       </c>
       <c r="K299" t="inlineStr"/>
@@ -19126,13 +19122,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>807.11</v>
+        <v>818.3</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>418-2482-CM26</t>
+          <t>3765-672-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19157,12 +19153,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.281-4</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -19172,22 +19168,26 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
-        </is>
-      </c>
-      <c r="K300" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>818.3</v>
+        <v>925.6799999999999</v>
       </c>
     </row>
     <row r="301">
@@ -19506,7 +19506,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2151-319-CM26</t>
+          <t>2151-320-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -19546,12 +19546,12 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
+          <t>DELTAMED LIMITADA</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>77.025.316-0</t>
+          <t>76.512.686-k</t>
         </is>
       </c>
       <c r="K306" t="inlineStr"/>
@@ -19561,7 +19561,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>1194.84</v>
+        <v>1843.42</v>
       </c>
     </row>
     <row r="307">
@@ -19632,7 +19632,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2151-320-CM26</t>
+          <t>2151-319-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -19672,12 +19672,12 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>DELTAMED LIMITADA</t>
+          <t>INGENIERIA, SOPORTE Y CADENA DE SUMINISTRO SPA</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>76.512.686-k</t>
+          <t>77.025.316-0</t>
         </is>
       </c>
       <c r="K308" t="inlineStr"/>
@@ -19687,13 +19687,13 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>1843.42</v>
+        <v>1194.84</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>418-2665-CM26</t>
+          <t>1692-576-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -19718,12 +19718,12 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.602.292-k</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -19733,32 +19733,28 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>MADEGOM S.A.</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>84.609.600-0</t>
-        </is>
-      </c>
-      <c r="K309" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.215.260-6</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr"/>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>2299.15</v>
+        <v>824.14</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>1692-576-CM26</t>
+          <t>1692-574-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -19798,12 +19794,12 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K310" t="inlineStr"/>
@@ -19813,13 +19809,13 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>824.14</v>
+        <v>823.88</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>1692-574-CM26</t>
+          <t>418-2665-CM26</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -19844,12 +19840,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>61.602.292-k</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE COCHRANE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -19859,22 +19855,26 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>MADEGOM S.A.</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
-        </is>
-      </c>
-      <c r="K311" t="inlineStr"/>
+          <t>84.609.600-0</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>823.88</v>
+        <v>2299.15</v>
       </c>
     </row>
     <row r="312">
@@ -20567,7 +20567,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>1691-1743-CM26</t>
+          <t>1691-1877-CM26</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -20626,13 +20626,13 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>24596.91</v>
+        <v>3383.96</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>1691-1877-CM26</t>
+          <t>1691-1743-CM26</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -20691,7 +20691,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>3383.96</v>
+        <v>24596.91</v>
       </c>
     </row>
     <row r="325">
@@ -21449,7 +21449,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>1691-1919-CM26</t>
+          <t>1691-2086-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -21489,12 +21489,12 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>MUNNICH PHARMA MEDICAL SPA</t>
+          <t>CLINICON SPA</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>80.447.400-5</t>
+          <t>77.070.635-1</t>
         </is>
       </c>
       <c r="K337" t="inlineStr"/>
@@ -21504,13 +21504,13 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>3210.57</v>
+        <v>2178.02</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>1691-2014-CM26</t>
+          <t>1691-2083-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -21569,7 +21569,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>1261.15</v>
+        <v>4978.37</v>
       </c>
     </row>
     <row r="339">
@@ -21636,7 +21636,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>1691-2083-CM26</t>
+          <t>1691-2014-CM26</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -21695,13 +21695,13 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>4978.37</v>
+        <v>1261.15</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>1691-2086-CM26</t>
+          <t>1691-1919-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -21741,12 +21741,12 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>CLINICON SPA</t>
+          <t>MUNNICH PHARMA MEDICAL SPA</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>77.070.635-1</t>
+          <t>80.447.400-5</t>
         </is>
       </c>
       <c r="K341" t="inlineStr"/>
@@ -21756,7 +21756,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>2178.02</v>
+        <v>3210.57</v>
       </c>
     </row>
     <row r="342">
@@ -21827,7 +21827,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>3950-1606-CM26</t>
+          <t>3950-1607-CM26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -21867,32 +21867,28 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>NEMO CHILE S.A.</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
-        </is>
-      </c>
-      <c r="K343" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.215.260-6</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr"/>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>5259.91</v>
+        <v>1071.98</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>3950-1607-CM26</t>
+          <t>3950-1606-CM26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -21932,22 +21928,26 @@
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>NEMO CHILE S.A.</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>76.215.260-6</t>
-        </is>
-      </c>
-      <c r="K344" t="inlineStr"/>
+          <t>81.210.400-4</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>1071.98</v>
+        <v>5259.91</v>
       </c>
     </row>
     <row r="345">
@@ -22075,7 +22075,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>1691-2182-CM26</t>
+          <t>1691-2188-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -22115,12 +22115,12 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>REUTTER S A</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>81.210.400-4</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
@@ -22134,13 +22134,13 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>2242.34</v>
+        <v>973.01</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>1691-2188-CM26</t>
+          <t>1691-2182-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -22180,12 +22180,12 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>REUTTER S A</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>81.210.400-4</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
@@ -22199,7 +22199,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>973.01</v>
+        <v>2242.34</v>
       </c>
     </row>
     <row r="349">
@@ -22261,6 +22261,128 @@
       </c>
       <c r="M349" s="2" t="n">
         <v>807.3200000000001</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>1691-2231-CM26</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>CONVATEC CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>76.020.266-5</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr"/>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M350" s="2" t="n">
+        <v>14953.85</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>1090323-27-CM26</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>2239-21-LR23</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>61.602.280-6</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>COMERCIAL MEDTRONIC CHILE LTDA</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>77.237.150-0</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr"/>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M351" s="2" t="n">
+        <v>15607.33</v>
       </c>
     </row>
   </sheetData>
